--- a/Översikt MARKARYD.xlsx
+++ b/Översikt MARKARYD.xlsx
@@ -601,7 +601,7 @@
         <v>45792</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45628</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44743</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>44818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>45219</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>44818</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>44956</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>45347</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>45453</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>45268</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>44553</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>46090</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>46203</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>45823</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>45876</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>44972</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>45581</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>45762</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>44879</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>44692</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>44467</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>44595</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>44700</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>44495</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         <v>44846</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>44802</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>44802</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>44802</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>44859</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>44474</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>44875</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>44638</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         <v>44460</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>44802</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>44802</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>44802</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>44582</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>44848</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>44837</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>44638</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>44700</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>44539</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>44587</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>44572</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>44642</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>44508</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>44700</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>44700</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>45236</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>45181</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>45119</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>45265</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         <v>45524</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         <v>44956</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>45054</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>44760</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>44839</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>44601</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>45419</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>45195</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>45079</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>44581</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>45434</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5862,7 +5862,7 @@
         <v>45539</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>45085</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>45434</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>44992</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>45582</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>44806</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>44875</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>45663</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>45329</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>44915</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>44601</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>45219</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>45602</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>45414</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>45195</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>44636</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>44988</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>44980</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>45426</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>45547</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>44970</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>44809</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>44557</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>45546</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>45141</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>45212</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>45258</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>45181</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>45008</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>44994</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>44536</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>45352</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>45069</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         <v>45191</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>45089</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>45216</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>44911</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>45281</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>44460</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         <v>44644</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>45512</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8880,7 +8880,7 @@
         <v>45219</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>45556</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>45666</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9099,7 +9099,7 @@
         <v>45530</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v>44467</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         <v>45219</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>44474</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>44798</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>45583</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         <v>45798</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>45063</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>45428</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>45281</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>45281</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         <v>44984</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9985,7 +9985,7 @@
         <v>45218</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>45903</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10131,7 +10131,7 @@
         <v>45909</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10209,7 +10209,7 @@
         <v>44928</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>45562</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10355,7 +10355,7 @@
         <v>45810</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10428,7 +10428,7 @@
         <v>45700</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10501,7 +10501,7 @@
         <v>45771</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         <v>44902</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>44516</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10720,7 +10720,7 @@
         <v>44677</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10793,7 +10793,7 @@
         <v>45917</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>44578</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>45532</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>45670</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>45678</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>45678</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11236,7 +11236,7 @@
         <v>45678</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         <v>45930</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>45930</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>45161</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>45643</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11601,7 +11601,7 @@
         <v>44606</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
         <v>44911</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11747,7 +11747,7 @@
         <v>45000</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>44935</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>44935</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>45473</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>44977</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>44977</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>45942</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12263,7 +12263,7 @@
         <v>44887</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
         <v>46149</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12409,7 +12409,7 @@
         <v>45614</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12482,7 +12482,7 @@
         <v>45225</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12555,7 +12555,7 @@
         <v>45236</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>45258</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>44565</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
         <v>44992</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>45267</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12920,7 +12920,7 @@
         <v>45265</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12993,7 +12993,7 @@
         <v>45265</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13066,7 +13066,7 @@
         <v>45203</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13139,7 +13139,7 @@
         <v>45980</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13212,7 +13212,7 @@
         <v>45378</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13285,7 +13285,7 @@
         <v>45181</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>45999</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13431,7 +13431,7 @@
         <v>45547</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13509,7 +13509,7 @@
         <v>44461</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         <v>44956</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13655,7 +13655,7 @@
         <v>44616</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
         <v>46155</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>45209</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
         <v>44958</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>45470</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>44818</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         <v>45160</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14166,7 +14166,7 @@
         <v>45092</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>46141</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14312,7 +14312,7 @@
         <v>45837</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14385,7 +14385,7 @@
         <v>46162</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>45678</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14531,7 +14531,7 @@
         <v>45678</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
         <v>45678</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14677,7 +14677,7 @@
         <v>45558</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14750,7 +14750,7 @@
         <v>44835</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>45266</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         <v>45281</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>45512</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15042,7 +15042,7 @@
         <v>45428</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>45077</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>45075</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>45680</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15344,7 +15344,7 @@
         <v>45275</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15422,7 +15422,7 @@
         <v>44823</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
         <v>46013</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
         <v>46013</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>46013</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>45155</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15787,7 +15787,7 @@
         <v>44999</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15860,7 +15860,7 @@
         <v>46021</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15933,7 +15933,7 @@
         <v>44579</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>45404</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16079,7 +16079,7 @@
         <v>45306</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>46168</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16225,7 +16225,7 @@
         <v>45281</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16298,7 +16298,7 @@
         <v>45040</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16371,7 +16371,7 @@
         <v>46034</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>45080</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>45021</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>46042</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16663,7 +16663,7 @@
         <v>44461</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>44992</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16809,7 +16809,7 @@
         <v>46049</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>46049</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16955,7 +16955,7 @@
         <v>46049</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         <v>45476</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17101,7 +17101,7 @@
         <v>45127</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17174,7 +17174,7 @@
         <v>46049</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>46175</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>44498</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17393,7 +17393,7 @@
         <v>45370</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
         <v>46062</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17539,7 +17539,7 @@
         <v>46063</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17612,7 +17612,7 @@
         <v>45357</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17685,7 +17685,7 @@
         <v>45361</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         <v>45191</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>45282</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>46069</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17982,7 +17982,7 @@
         <v>45026</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>46069</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18133,7 +18133,7 @@
         <v>46069</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>46069</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18289,7 +18289,7 @@
         <v>45218</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18362,7 +18362,7 @@
         <v>46069</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18440,7 +18440,7 @@
         <v>45117</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18518,7 +18518,7 @@
         <v>44700</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18591,7 +18591,7 @@
         <v>45281</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>45240</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>45625</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18815,7 +18815,7 @@
         <v>46085</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>46085</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         <v>46085</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>46085</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>46085</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>46090</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>45196</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>44902</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19404,7 +19404,7 @@
         <v>45268</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>46090</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19560,7 +19560,7 @@
         <v>46090</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19638,7 +19638,7 @@
         <v>46090</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>46090</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19794,7 +19794,7 @@
         <v>46090</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19872,7 +19872,7 @@
         <v>46190</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19945,7 +19945,7 @@
         <v>45296</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20018,7 +20018,7 @@
         <v>46190</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20091,7 +20091,7 @@
         <v>44790</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20164,7 +20164,7 @@
         <v>44587</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20237,7 +20237,7 @@
         <v>45085</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20310,7 +20310,7 @@
         <v>44498</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20383,7 +20383,7 @@
         <v>44601</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>44601</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>46100</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>46100</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20685,7 +20685,7 @@
         <v>44572</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>46100</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20831,7 +20831,7 @@
         <v>45141</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20909,7 +20909,7 @@
         <v>45407</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20982,7 +20982,7 @@
         <v>45054</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21055,7 +21055,7 @@
         <v>45069</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21128,7 +21128,7 @@
         <v>46111</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>45210</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21274,7 +21274,7 @@
         <v>45707</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>45282</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21420,7 +21420,7 @@
         <v>46244</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
         <v>45593</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21571,7 +21571,7 @@
         <v>44531</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21644,7 +21644,7 @@
         <v>45166</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21717,7 +21717,7 @@
         <v>46129</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21790,7 +21790,7 @@
         <v>46133</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21863,7 +21863,7 @@
         <v>45687</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21936,7 +21936,7 @@
         <v>44844</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>45371</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22087,7 +22087,7 @@
         <v>45230</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
         <v>45564</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         <v>45837</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22306,7 +22306,7 @@
         <v>45257</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
         <v>45923</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22452,7 +22452,7 @@
         <v>45090</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>45217</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
         <v>45372</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>45678</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22744,7 +22744,7 @@
         <v>44581</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22817,7 +22817,7 @@
         <v>44553</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22890,7 +22890,7 @@
         <v>46206</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>44810</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23036,7 +23036,7 @@
         <v>45671</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>46210</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>45344</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23260,7 +23260,7 @@
         <v>44848</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23333,7 +23333,7 @@
         <v>45678</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23406,7 +23406,7 @@
         <v>45230</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23479,7 +23479,7 @@
         <v>44463</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23552,7 +23552,7 @@
         <v>45258</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>45080</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23698,7 +23698,7 @@
         <v>44984</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23771,7 +23771,7 @@
         <v>45275</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23849,7 +23849,7 @@
         <v>46213</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23922,7 +23922,7 @@
         <v>44950</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23995,7 +23995,7 @@
         <v>45681</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24068,7 +24068,7 @@
         <v>45462</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>45372</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24214,7 +24214,7 @@
         <v>45566</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         <v>45400</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24360,7 +24360,7 @@
         <v>45173</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24433,7 +24433,7 @@
         <v>45306</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24506,7 +24506,7 @@
         <v>45428</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>45628</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24652,7 +24652,7 @@
         <v>46267</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24725,7 +24725,7 @@
         <v>45265</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24798,7 +24798,7 @@
         <v>46269</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24871,7 +24871,7 @@
         <v>46269</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24944,7 +24944,7 @@
         <v>46269</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25017,7 +25017,7 @@
         <v>45230</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         <v>45607</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25163,7 +25163,7 @@
         <v>45581</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25236,7 +25236,7 @@
         <v>45783</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25309,7 +25309,7 @@
         <v>45609</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25382,7 +25382,7 @@
         <v>45637</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25460,7 +25460,7 @@
         <v>45637</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>45609</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>45609</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25684,7 +25684,7 @@
         <v>45444</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25757,7 +25757,7 @@
         <v>45232</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25830,7 +25830,7 @@
         <v>45593</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25908,7 +25908,7 @@
         <v>45600</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>46281</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26054,7 +26054,7 @@
         <v>45792</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26127,7 +26127,7 @@
         <v>45797</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26205,7 +26205,7 @@
         <v>46282</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26278,7 +26278,7 @@
         <v>46240</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26356,7 +26356,7 @@
         <v>46240</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26434,7 +26434,7 @@
         <v>46282</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         <v>45800</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26580,7 +26580,7 @@
         <v>45800</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26653,7 +26653,7 @@
         <v>45237</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26726,7 +26726,7 @@
         <v>45418</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -26799,7 +26799,7 @@
         <v>45842</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -26872,7 +26872,7 @@
         <v>45842</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -26945,7 +26945,7 @@
         <v>45107</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27023,7 +27023,7 @@
         <v>45719</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>45882</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>45769</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27242,7 +27242,7 @@
         <v>45170</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27315,7 +27315,7 @@
         <v>44673</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>44673</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27461,7 +27461,7 @@
         <v>45769</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>45874</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27607,7 +27607,7 @@
         <v>45880</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27680,7 +27680,7 @@
         <v>45880</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>45218</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -27826,7 +27826,7 @@
         <v>45014</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -27899,7 +27899,7 @@
         <v>45551</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -27972,7 +27972,7 @@
         <v>44621</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28045,7 +28045,7 @@
         <v>44858</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28118,7 +28118,7 @@
         <v>45002</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28191,7 +28191,7 @@
         <v>45470</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         <v>44978</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28337,7 +28337,7 @@
         <v>45721</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28410,7 +28410,7 @@
         <v>45792</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28483,7 +28483,7 @@
         <v>45814</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -28556,7 +28556,7 @@
         <v>45880</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -28629,7 +28629,7 @@
         <v>46049</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>

--- a/Översikt MARKARYD.xlsx
+++ b/Översikt MARKARYD.xlsx
@@ -601,7 +601,7 @@
         <v>45792</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45628</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44743</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>44818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>45219</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>44818</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>45453</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>44553</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>46090</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>45268</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>45347</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>45823</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>45876</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>46203</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>44956</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>44972</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>45581</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>45762</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>44879</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>44692</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>44467</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>44595</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>44700</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>44495</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         <v>44846</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>44802</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>44802</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>44802</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>44859</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>44474</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>44875</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>44638</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         <v>44802</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>44802</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>44802</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>44582</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>44848</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>44837</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>44638</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>44700</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>44539</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>44587</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>44572</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>44642</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>44508</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>44700</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>44700</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>44988</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>45275</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>45771</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>45196</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>45054</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         <v>45512</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
         <v>44810</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>45008</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>45546</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>45414</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>45069</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>45371</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>44823</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>45219</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>45426</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         <v>45217</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         <v>45370</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         <v>45428</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
         <v>45378</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>45265</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         <v>44474</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>44806</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>46013</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>45040</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>45265</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>46021</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>45419</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>45275</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>44848</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>45266</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>45797</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>46034</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>45218</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>45530</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>45539</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>44835</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>44498</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>45085</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>45800</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>45800</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>46042</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>44579</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>46049</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         <v>46049</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>46049</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         <v>46049</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>44875</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         <v>44498</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         <v>45903</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>44587</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>45357</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>45361</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>45909</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>45700</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         <v>45556</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>45810</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         <v>45216</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>45562</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         <v>46062</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>45917</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>46063</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>44557</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9235,7 +9235,7 @@
         <v>46069</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>44565</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>45127</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         <v>46069</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>46069</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>46069</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>46069</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
         <v>44950</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9844,7 +9844,7 @@
         <v>45026</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         <v>45687</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         <v>45930</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>45372</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>46085</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10209,7 +10209,7 @@
         <v>46085</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>46085</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10355,7 +10355,7 @@
         <v>45583</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10428,7 +10428,7 @@
         <v>46085</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10501,7 +10501,7 @@
         <v>46085</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         <v>46090</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>46090</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>46090</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>46090</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         <v>46090</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         <v>46090</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>45678</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
         <v>45678</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
         <v>45678</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11261,7 +11261,7 @@
         <v>45209</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>44984</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11407,7 +11407,7 @@
         <v>44977</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>45942</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11553,7 +11553,7 @@
         <v>46100</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         <v>45089</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>46100</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11772,7 +11772,7 @@
         <v>46100</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11845,7 +11845,7 @@
         <v>45219</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>45707</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11991,7 +11991,7 @@
         <v>45434</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12064,7 +12064,7 @@
         <v>45282</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         <v>46111</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>45267</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>45258</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>45079</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         <v>45080</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>44984</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12575,7 +12575,7 @@
         <v>45237</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>46129</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         <v>44992</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         <v>45473</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>45680</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12940,7 +12940,7 @@
         <v>44956</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13013,7 +13013,7 @@
         <v>45678</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>45678</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         <v>45678</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>45663</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13305,7 +13305,7 @@
         <v>46133</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13378,7 +13378,7 @@
         <v>45614</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13451,7 +13451,7 @@
         <v>44798</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>45837</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>44977</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13670,7 +13670,7 @@
         <v>45798</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
         <v>45092</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>45476</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13889,7 +13889,7 @@
         <v>44839</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13967,7 +13967,7 @@
         <v>45666</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>46013</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>46013</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>45212</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>45564</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>45923</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
         <v>45203</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>45075</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14556,7 +14556,7 @@
         <v>44994</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
         <v>45532</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14702,7 +14702,7 @@
         <v>45281</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>44844</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>45670</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>45418</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14999,7 +14999,7 @@
         <v>46149</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
         <v>44902</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15145,7 +15145,7 @@
         <v>45077</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>44467</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15291,7 +15291,7 @@
         <v>44970</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15364,7 +15364,7 @@
         <v>45980</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15437,7 +15437,7 @@
         <v>45558</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>44915</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15583,7 +15583,7 @@
         <v>45999</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>46155</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15729,7 +15729,7 @@
         <v>45344</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15802,7 +15802,7 @@
         <v>45265</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15875,7 +15875,7 @@
         <v>46141</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15948,7 +15948,7 @@
         <v>45054</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16021,7 +16021,7 @@
         <v>46162</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16094,7 +16094,7 @@
         <v>45837</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16167,7 +16167,7 @@
         <v>45161</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>45842</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16313,7 +16313,7 @@
         <v>45069</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>45842</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16459,7 +16459,7 @@
         <v>45719</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>45107</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         <v>45281</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16683,7 +16683,7 @@
         <v>46168</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
         <v>44572</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>45258</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16902,7 +16902,7 @@
         <v>45258</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16975,7 +16975,7 @@
         <v>45063</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>45329</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>46175</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17194,7 +17194,7 @@
         <v>45021</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>44992</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17340,7 +17340,7 @@
         <v>45882</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17413,7 +17413,7 @@
         <v>45524</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>45306</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>45166</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>45593</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>45769</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>44636</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
         <v>45141</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>45582</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>45170</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>45769</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18153,7 +18153,7 @@
         <v>44516</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>45547</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>44673</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18377,7 +18377,7 @@
         <v>44673</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18450,7 +18450,7 @@
         <v>45191</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>45085</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>46190</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>46190</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>45874</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18815,7 +18815,7 @@
         <v>45512</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>45880</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         <v>44536</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>45880</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>45218</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>44581</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>45230</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19326,7 +19326,7 @@
         <v>46206</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         <v>45090</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>46210</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>45191</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19623,7 +19623,7 @@
         <v>45678</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19696,7 +19696,7 @@
         <v>45117</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19774,7 +19774,7 @@
         <v>45434</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19847,7 +19847,7 @@
         <v>45625</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19920,7 +19920,7 @@
         <v>45141</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19993,7 +19993,7 @@
         <v>44677</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20066,7 +20066,7 @@
         <v>45080</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20139,7 +20139,7 @@
         <v>46213</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20212,7 +20212,7 @@
         <v>44818</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>45181</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20358,7 +20358,7 @@
         <v>45181</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20436,7 +20436,7 @@
         <v>45160</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20509,7 +20509,7 @@
         <v>45681</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20582,7 +20582,7 @@
         <v>45400</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20655,7 +20655,7 @@
         <v>45181</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>45219</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20806,7 +20806,7 @@
         <v>45643</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20879,7 +20879,7 @@
         <v>44790</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20952,7 +20952,7 @@
         <v>45281</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>46267</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>45296</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>45306</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>46269</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>46269</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>45257</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21468,7 +21468,7 @@
         <v>45230</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21541,7 +21541,7 @@
         <v>45281</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21614,7 +21614,7 @@
         <v>46269</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21687,7 +21687,7 @@
         <v>45240</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>45173</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21833,7 +21833,7 @@
         <v>45265</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>45268</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21984,7 +21984,7 @@
         <v>45195</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22057,7 +22057,7 @@
         <v>46282</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
         <v>46240</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>45236</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22281,7 +22281,7 @@
         <v>46282</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>46240</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>46281</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22505,7 +22505,7 @@
         <v>46244</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22583,7 +22583,7 @@
         <v>45628</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>44935</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>44935</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>44553</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>44911</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>45000</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23026,7 +23026,7 @@
         <v>44601</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23104,7 +23104,7 @@
         <v>44606</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23177,7 +23177,7 @@
         <v>44581</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23250,7 +23250,7 @@
         <v>44531</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23323,7 +23323,7 @@
         <v>44809</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23396,7 +23396,7 @@
         <v>45566</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23469,7 +23469,7 @@
         <v>44992</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>46288</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23615,7 +23615,7 @@
         <v>45119</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23688,7 +23688,7 @@
         <v>45281</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23761,7 +23761,7 @@
         <v>45281</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23834,7 +23834,7 @@
         <v>46290</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23907,7 +23907,7 @@
         <v>44644</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23980,7 +23980,7 @@
         <v>45236</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24053,7 +24053,7 @@
         <v>45462</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24126,7 +24126,7 @@
         <v>44887</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24199,7 +24199,7 @@
         <v>44578</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24277,7 +24277,7 @@
         <v>45602</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>45428</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24428,7 +24428,7 @@
         <v>44616</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         <v>44902</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>44760</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24647,7 +24647,7 @@
         <v>44911</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24720,7 +24720,7 @@
         <v>44601</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24798,7 +24798,7 @@
         <v>44601</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24876,7 +24876,7 @@
         <v>44700</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24949,7 +24949,7 @@
         <v>45678</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25022,7 +25022,7 @@
         <v>45218</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25095,7 +25095,7 @@
         <v>45470</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>45225</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25241,7 +25241,7 @@
         <v>44928</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25314,7 +25314,7 @@
         <v>44956</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25387,7 +25387,7 @@
         <v>45372</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25460,7 +25460,7 @@
         <v>45282</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25533,7 +25533,7 @@
         <v>45404</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25606,7 +25606,7 @@
         <v>44958</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25679,7 +25679,7 @@
         <v>45547</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25757,7 +25757,7 @@
         <v>45195</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25830,7 +25830,7 @@
         <v>45671</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25903,7 +25903,7 @@
         <v>45155</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         <v>45210</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26049,7 +26049,7 @@
         <v>44980</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>44601</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26200,7 +26200,7 @@
         <v>45407</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26273,7 +26273,7 @@
         <v>45352</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>45428</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26424,7 +26424,7 @@
         <v>44999</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26497,7 +26497,7 @@
         <v>45230</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26570,7 +26570,7 @@
         <v>45607</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
         <v>45581</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26716,7 +26716,7 @@
         <v>45783</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>45609</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -26862,7 +26862,7 @@
         <v>45609</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>45609</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27008,7 +27008,7 @@
         <v>45637</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27086,7 +27086,7 @@
         <v>45637</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27164,7 +27164,7 @@
         <v>45444</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27237,7 +27237,7 @@
         <v>45600</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27310,7 +27310,7 @@
         <v>45593</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>45232</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27461,7 +27461,7 @@
         <v>45792</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>44621</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27607,7 +27607,7 @@
         <v>45014</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27680,7 +27680,7 @@
         <v>45551</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>44858</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -27826,7 +27826,7 @@
         <v>45002</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -27899,7 +27899,7 @@
         <v>45470</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -27972,7 +27972,7 @@
         <v>44978</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28045,7 +28045,7 @@
         <v>45721</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28118,7 +28118,7 @@
         <v>45792</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28191,7 +28191,7 @@
         <v>45814</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         <v>45880</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28337,7 +28337,7 @@
         <v>46049</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>

--- a/Översikt MARKARYD.xlsx
+++ b/Översikt MARKARYD.xlsx
@@ -601,7 +601,7 @@
         <v>45792</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45628</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44743</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>44818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>45219</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>44818</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>45453</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>44553</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>46090</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>45268</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>45347</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>45823</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>45876</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>46203</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>44956</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>44972</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>45581</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>45762</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>44879</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>44692</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>44467</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>44595</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>44700</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>44495</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         <v>44846</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>44802</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>44802</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>44802</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>44859</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>44474</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>44875</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>44638</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         <v>44802</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>44802</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>44802</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>44582</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>44848</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>44837</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>44638</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>44700</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>44539</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>44587</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>44572</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>44642</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>44508</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>44700</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>44700</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>44988</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>45275</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>45771</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>45196</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>45054</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         <v>45512</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
         <v>44810</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>45008</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>45546</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>45414</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>45069</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>45371</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>44823</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>45219</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>45426</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         <v>45217</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         <v>45370</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         <v>45428</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
         <v>45378</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>45265</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         <v>44474</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>44806</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>46013</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>45040</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>45265</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>46021</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>45419</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>45275</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>44848</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>45266</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>45797</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>46034</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>45218</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>45530</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>45539</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7259,7 +7259,7 @@
         <v>44835</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>44498</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>45085</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>45800</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>45800</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>46042</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>44579</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>46049</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         <v>46049</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>46049</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         <v>46049</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>44875</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         <v>44498</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         <v>45903</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>44587</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>45357</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>45361</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>45909</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>45700</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         <v>45556</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>45810</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         <v>45216</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>45562</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         <v>46062</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>45917</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>46063</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>44557</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9235,7 +9235,7 @@
         <v>46069</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>44565</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>45127</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         <v>46069</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>46069</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>46069</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>46069</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
         <v>44950</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9844,7 +9844,7 @@
         <v>45026</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         <v>45687</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         <v>45930</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>45372</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>46085</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10209,7 +10209,7 @@
         <v>46085</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>46085</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10355,7 +10355,7 @@
         <v>45583</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10428,7 +10428,7 @@
         <v>46085</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10501,7 +10501,7 @@
         <v>46085</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         <v>46090</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>46090</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>46090</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>46090</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         <v>46090</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         <v>46090</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>45678</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
         <v>45678</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
         <v>45678</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11261,7 +11261,7 @@
         <v>45209</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>44984</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11407,7 +11407,7 @@
         <v>44977</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>45942</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11553,7 +11553,7 @@
         <v>46100</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         <v>45089</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>46100</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11772,7 +11772,7 @@
         <v>46100</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11845,7 +11845,7 @@
         <v>45219</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
         <v>45707</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11991,7 +11991,7 @@
         <v>45434</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12064,7 +12064,7 @@
         <v>45282</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         <v>46111</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>45267</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>45258</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>45079</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         <v>45080</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>44984</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12575,7 +12575,7 @@
         <v>45237</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12648,7 +12648,7 @@
         <v>46129</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         <v>44992</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         <v>45473</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>45680</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12940,7 +12940,7 @@
         <v>44956</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13013,7 +13013,7 @@
         <v>45678</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>45678</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         <v>45678</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>45663</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13305,7 +13305,7 @@
         <v>46133</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13378,7 +13378,7 @@
         <v>45614</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13451,7 +13451,7 @@
         <v>44798</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13524,7 +13524,7 @@
         <v>45837</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>44977</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13670,7 +13670,7 @@
         <v>45798</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
         <v>45092</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>45476</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13889,7 +13889,7 @@
         <v>44839</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13967,7 +13967,7 @@
         <v>45666</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>46013</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>46013</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>45212</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>45564</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>45923</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
         <v>45203</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>45075</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14556,7 +14556,7 @@
         <v>44994</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
         <v>45532</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14702,7 +14702,7 @@
         <v>45281</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>44844</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>45670</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>45418</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14999,7 +14999,7 @@
         <v>46149</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
         <v>44902</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15145,7 +15145,7 @@
         <v>45077</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>44467</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15291,7 +15291,7 @@
         <v>44970</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15364,7 +15364,7 @@
         <v>45980</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15437,7 +15437,7 @@
         <v>45558</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>44915</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15583,7 +15583,7 @@
         <v>45999</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>46155</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15729,7 +15729,7 @@
         <v>45344</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15802,7 +15802,7 @@
         <v>45265</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15875,7 +15875,7 @@
         <v>46141</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15948,7 +15948,7 @@
         <v>45054</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16021,7 +16021,7 @@
         <v>46162</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16094,7 +16094,7 @@
         <v>45837</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16167,7 +16167,7 @@
         <v>45161</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>45842</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16313,7 +16313,7 @@
         <v>45069</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>45842</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16459,7 +16459,7 @@
         <v>45719</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>45107</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         <v>45281</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16683,7 +16683,7 @@
         <v>46168</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
         <v>44572</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>45258</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16902,7 +16902,7 @@
         <v>45258</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16975,7 +16975,7 @@
         <v>45063</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>45329</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>46175</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17194,7 +17194,7 @@
         <v>45021</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>44992</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17340,7 +17340,7 @@
         <v>45882</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17413,7 +17413,7 @@
         <v>45524</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>45306</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>45166</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>45593</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>45769</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>44636</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
         <v>45141</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>45582</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>45170</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>45769</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18153,7 +18153,7 @@
         <v>44516</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>45547</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>44673</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18377,7 +18377,7 @@
         <v>44673</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18450,7 +18450,7 @@
         <v>45191</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18523,7 +18523,7 @@
         <v>45085</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>46190</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>46190</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>45874</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18815,7 +18815,7 @@
         <v>45512</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>45880</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         <v>44536</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>45880</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>45218</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>44581</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>45230</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19326,7 +19326,7 @@
         <v>46206</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         <v>45090</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>46210</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>45191</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19623,7 +19623,7 @@
         <v>45678</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19696,7 +19696,7 @@
         <v>45117</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19774,7 +19774,7 @@
         <v>45434</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19847,7 +19847,7 @@
         <v>45625</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19920,7 +19920,7 @@
         <v>45141</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19993,7 +19993,7 @@
         <v>44677</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20066,7 +20066,7 @@
         <v>45080</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20139,7 +20139,7 @@
         <v>46213</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20212,7 +20212,7 @@
         <v>44818</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>45181</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20358,7 +20358,7 @@
         <v>45181</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20436,7 +20436,7 @@
         <v>45160</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20509,7 +20509,7 @@
         <v>45681</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20582,7 +20582,7 @@
         <v>45400</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20655,7 +20655,7 @@
         <v>45181</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>45219</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20806,7 +20806,7 @@
         <v>45643</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20879,7 +20879,7 @@
         <v>44790</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20952,7 +20952,7 @@
         <v>45281</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>46267</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>45296</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>45306</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>46269</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>46269</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>45257</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21468,7 +21468,7 @@
         <v>45230</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21541,7 +21541,7 @@
         <v>45281</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21614,7 +21614,7 @@
         <v>46269</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21687,7 +21687,7 @@
         <v>45240</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>45173</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21833,7 +21833,7 @@
         <v>45265</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>45268</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21984,7 +21984,7 @@
         <v>45195</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22057,7 +22057,7 @@
         <v>46282</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
         <v>46240</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>45236</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22281,7 +22281,7 @@
         <v>46282</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>46240</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>46281</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22505,7 +22505,7 @@
         <v>46244</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22583,7 +22583,7 @@
         <v>45628</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>44935</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>44935</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>44553</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>44911</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>45000</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23026,7 +23026,7 @@
         <v>44601</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23104,7 +23104,7 @@
         <v>44606</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23177,7 +23177,7 @@
         <v>44581</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23250,7 +23250,7 @@
         <v>44531</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23323,7 +23323,7 @@
         <v>44809</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23396,7 +23396,7 @@
         <v>45566</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23469,7 +23469,7 @@
         <v>44992</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>46288</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23615,7 +23615,7 @@
         <v>45119</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23688,7 +23688,7 @@
         <v>45281</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23761,7 +23761,7 @@
         <v>45281</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23834,7 +23834,7 @@
         <v>46290</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23907,7 +23907,7 @@
         <v>44644</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23980,7 +23980,7 @@
         <v>45236</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24053,7 +24053,7 @@
         <v>45462</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24126,7 +24126,7 @@
         <v>44887</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24199,7 +24199,7 @@
         <v>44578</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24277,7 +24277,7 @@
         <v>45602</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>45428</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24428,7 +24428,7 @@
         <v>44616</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         <v>44902</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>44760</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24647,7 +24647,7 @@
         <v>44911</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24720,7 +24720,7 @@
         <v>44601</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24798,7 +24798,7 @@
         <v>44601</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24876,7 +24876,7 @@
         <v>44700</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24949,7 +24949,7 @@
         <v>45678</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25022,7 +25022,7 @@
         <v>45218</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25095,7 +25095,7 @@
         <v>45470</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>45225</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25241,7 +25241,7 @@
         <v>44928</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25314,7 +25314,7 @@
         <v>44956</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25387,7 +25387,7 @@
         <v>45372</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25460,7 +25460,7 @@
         <v>45282</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25533,7 +25533,7 @@
         <v>45404</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25606,7 +25606,7 @@
         <v>44958</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25679,7 +25679,7 @@
         <v>45547</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25757,7 +25757,7 @@
         <v>45195</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25830,7 +25830,7 @@
         <v>45671</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25903,7 +25903,7 @@
         <v>45155</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         <v>45210</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26049,7 +26049,7 @@
         <v>44980</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>44601</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26200,7 +26200,7 @@
         <v>45407</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26273,7 +26273,7 @@
         <v>45352</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>45428</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26424,7 +26424,7 @@
         <v>44999</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26497,7 +26497,7 @@
         <v>45230</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26570,7 +26570,7 @@
         <v>45607</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
         <v>45581</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26716,7 +26716,7 @@
         <v>45783</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>45609</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -26862,7 +26862,7 @@
         <v>45609</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>45609</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27008,7 +27008,7 @@
         <v>45637</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27086,7 +27086,7 @@
         <v>45637</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27164,7 +27164,7 @@
         <v>45444</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27237,7 +27237,7 @@
         <v>45600</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27310,7 +27310,7 @@
         <v>45593</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>45232</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27461,7 +27461,7 @@
         <v>45792</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>44621</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27607,7 +27607,7 @@
         <v>45014</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27680,7 +27680,7 @@
         <v>45551</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>44858</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -27826,7 +27826,7 @@
         <v>45002</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -27899,7 +27899,7 @@
         <v>45470</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -27972,7 +27972,7 @@
         <v>44978</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28045,7 +28045,7 @@
         <v>45721</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28118,7 +28118,7 @@
         <v>45792</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28191,7 +28191,7 @@
         <v>45814</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         <v>45880</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28337,7 +28337,7 @@
         <v>46049</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>

--- a/Översikt MARKARYD.xlsx
+++ b/Översikt MARKARYD.xlsx
@@ -601,7 +601,7 @@
         <v>45792</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45628</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44743</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>44818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>45219</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>44818</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>44956</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>45347</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>46090</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>45453</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>45268</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>45823</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>45876</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>46203</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>44553</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>44972</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>45581</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>45762</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>44879</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>44692</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>44595</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>44700</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>44495</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>44846</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         <v>44802</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>44802</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>44802</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>44859</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>44474</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>44875</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>44638</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>44802</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         <v>44802</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>44802</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>44582</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>44848</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>44837</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>44638</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>44700</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>44539</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>44642</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>44572</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>44587</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>44508</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>44700</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>44700</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>45236</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>44760</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>45119</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>45181</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>45079</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>44581</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         <v>45524</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         <v>45265</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>44956</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>45054</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>44839</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>44601</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>45419</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>45593</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>45434</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>45600</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>45195</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>45434</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>45218</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>45539</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>45414</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>45085</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>46013</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>46013</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>46013</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>44992</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>46021</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>45582</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>44806</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>44875</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>45663</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>45329</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>46034</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>45219</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>45903</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>45909</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>44915</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>46042</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>44601</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>45602</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         <v>45792</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>45810</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>45700</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>45797</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>46049</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>46049</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>45195</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>45917</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>44636</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>44988</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         <v>45800</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>45800</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>45212</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>44980</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>45547</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>45426</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>44970</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>46062</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8885,7 +8885,7 @@
         <v>46063</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>44557</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>45930</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>45546</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9182,7 +9182,7 @@
         <v>46069</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>44809</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>46069</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>46069</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         <v>46069</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>46069</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>45141</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>45942</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>45258</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>45181</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>46085</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>46085</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>46085</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>46085</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>46085</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>46090</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>45008</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         <v>46090</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>46090</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>46090</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>46090</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
         <v>46090</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10848,7 +10848,7 @@
         <v>44994</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>45191</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>44536</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>45069</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>45352</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         <v>46100</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>46100</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11359,7 +11359,7 @@
         <v>46100</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
         <v>45089</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>45216</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>44911</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11651,7 +11651,7 @@
         <v>45281</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>44644</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>45237</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>46111</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11943,7 +11943,7 @@
         <v>45512</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         <v>45219</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12089,7 +12089,7 @@
         <v>45556</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>45530</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12240,7 +12240,7 @@
         <v>45418</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>46129</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>46133</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
         <v>45219</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>44474</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>44798</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>45583</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12751,7 +12751,7 @@
         <v>45564</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>45837</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
         <v>45063</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
         <v>45428</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>45923</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>45281</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>45281</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>45842</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>44984</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>45842</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>45107</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13564,7 +13564,7 @@
         <v>45719</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>45666</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13710,7 +13710,7 @@
         <v>44928</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>45562</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         <v>45771</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13929,7 +13929,7 @@
         <v>44902</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>44516</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14075,7 +14075,7 @@
         <v>44677</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>44578</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14226,7 +14226,7 @@
         <v>45798</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
         <v>45670</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14372,7 +14372,7 @@
         <v>45678</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14445,7 +14445,7 @@
         <v>45678</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14518,7 +14518,7 @@
         <v>45678</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14591,7 +14591,7 @@
         <v>45161</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>45643</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>44606</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14810,7 +14810,7 @@
         <v>44911</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14883,7 +14883,7 @@
         <v>45000</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         <v>44935</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>44935</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>45473</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
         <v>44977</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>44977</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>45882</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>45769</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15472,7 +15472,7 @@
         <v>44887</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>45532</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>45614</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15691,7 +15691,7 @@
         <v>45225</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15764,7 +15764,7 @@
         <v>45236</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15837,7 +15837,7 @@
         <v>45258</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>44565</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15983,7 +15983,7 @@
         <v>45170</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>46149</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16129,7 +16129,7 @@
         <v>44673</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>44673</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>45769</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16348,7 +16348,7 @@
         <v>44992</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>45267</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>45265</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16567,7 +16567,7 @@
         <v>45874</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16640,7 +16640,7 @@
         <v>45265</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>45980</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16786,7 +16786,7 @@
         <v>45999</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>45203</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16932,7 +16932,7 @@
         <v>46155</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>45378</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>46141</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17151,7 +17151,7 @@
         <v>45181</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17224,7 +17224,7 @@
         <v>45837</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17297,7 +17297,7 @@
         <v>46162</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17370,7 +17370,7 @@
         <v>45547</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>44956</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>45880</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>44616</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>45209</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
         <v>44958</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>45470</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17886,7 +17886,7 @@
         <v>45880</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>46168</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18032,7 +18032,7 @@
         <v>44818</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         <v>45160</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>45092</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>45218</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18324,7 +18324,7 @@
         <v>46175</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>45678</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>45678</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18543,7 +18543,7 @@
         <v>45678</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18616,7 +18616,7 @@
         <v>45558</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>44835</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>45266</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18835,7 +18835,7 @@
         <v>45281</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18908,7 +18908,7 @@
         <v>45512</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>45428</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>45077</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19132,7 +19132,7 @@
         <v>46190</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>45075</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>45680</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
         <v>45275</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19434,7 +19434,7 @@
         <v>44823</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19507,7 +19507,7 @@
         <v>45155</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19580,7 +19580,7 @@
         <v>44999</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
         <v>44579</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19726,7 +19726,7 @@
         <v>45404</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         <v>45306</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19872,7 +19872,7 @@
         <v>45281</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19945,7 +19945,7 @@
         <v>45040</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20018,7 +20018,7 @@
         <v>45080</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20091,7 +20091,7 @@
         <v>45021</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20164,7 +20164,7 @@
         <v>46206</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20237,7 +20237,7 @@
         <v>46210</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>44992</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20388,7 +20388,7 @@
         <v>45476</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>45127</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20534,7 +20534,7 @@
         <v>46213</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20607,7 +20607,7 @@
         <v>44498</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20680,7 +20680,7 @@
         <v>45370</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20753,7 +20753,7 @@
         <v>45357</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20826,7 +20826,7 @@
         <v>45361</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20899,7 +20899,7 @@
         <v>45191</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20972,7 +20972,7 @@
         <v>45282</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21045,7 +21045,7 @@
         <v>46267</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21118,7 +21118,7 @@
         <v>45026</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21191,7 +21191,7 @@
         <v>45218</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21264,7 +21264,7 @@
         <v>46269</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21337,7 +21337,7 @@
         <v>46269</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21410,7 +21410,7 @@
         <v>45117</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>44700</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>46269</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21634,7 +21634,7 @@
         <v>45281</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21712,7 +21712,7 @@
         <v>45240</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21785,7 +21785,7 @@
         <v>45625</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21858,7 +21858,7 @@
         <v>45196</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44902</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
         <v>46281</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22077,7 +22077,7 @@
         <v>45268</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>45296</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22228,7 +22228,7 @@
         <v>44790</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22301,7 +22301,7 @@
         <v>44587</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>45085</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22447,7 +22447,7 @@
         <v>44498</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22520,7 +22520,7 @@
         <v>46282</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22593,7 +22593,7 @@
         <v>44601</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>44601</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22749,7 +22749,7 @@
         <v>46240</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22827,7 +22827,7 @@
         <v>44572</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22900,7 +22900,7 @@
         <v>46240</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22978,7 +22978,7 @@
         <v>46282</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23051,7 +23051,7 @@
         <v>45141</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>46244</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23207,7 +23207,7 @@
         <v>45407</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23280,7 +23280,7 @@
         <v>45054</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>45069</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>45210</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>46288</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>45707</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>45282</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>46290</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23791,7 +23791,7 @@
         <v>45593</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23864,7 +23864,7 @@
         <v>44531</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23937,7 +23937,7 @@
         <v>45166</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24010,7 +24010,7 @@
         <v>45687</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24083,7 +24083,7 @@
         <v>44844</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24161,7 +24161,7 @@
         <v>45371</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24234,7 +24234,7 @@
         <v>45230</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24307,7 +24307,7 @@
         <v>45257</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24380,7 +24380,7 @@
         <v>46297</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24453,7 +24453,7 @@
         <v>45090</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24526,7 +24526,7 @@
         <v>45217</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>45372</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24672,7 +24672,7 @@
         <v>46297</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>45678</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24818,7 +24818,7 @@
         <v>46297</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24891,7 +24891,7 @@
         <v>44581</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24964,7 +24964,7 @@
         <v>44553</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25037,7 +25037,7 @@
         <v>44810</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>45671</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         <v>45344</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25256,7 +25256,7 @@
         <v>44848</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>45678</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25402,7 +25402,7 @@
         <v>45230</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25475,7 +25475,7 @@
         <v>45258</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>45080</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25621,7 +25621,7 @@
         <v>44984</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25694,7 +25694,7 @@
         <v>45275</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>44950</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25845,7 +25845,7 @@
         <v>45681</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25918,7 +25918,7 @@
         <v>45462</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -25991,7 +25991,7 @@
         <v>45372</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26064,7 +26064,7 @@
         <v>45566</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26137,7 +26137,7 @@
         <v>45400</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26210,7 +26210,7 @@
         <v>45173</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26283,7 +26283,7 @@
         <v>45306</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26356,7 +26356,7 @@
         <v>45428</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>45628</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26502,7 +26502,7 @@
         <v>45265</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26575,7 +26575,7 @@
         <v>45230</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26648,7 +26648,7 @@
         <v>45607</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26721,7 +26721,7 @@
         <v>45581</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -26794,7 +26794,7 @@
         <v>45783</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         <v>45609</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -26940,7 +26940,7 @@
         <v>45637</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27018,7 +27018,7 @@
         <v>45637</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>45609</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>45609</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27242,7 +27242,7 @@
         <v>45444</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27315,7 +27315,7 @@
         <v>45232</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>45014</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27461,7 +27461,7 @@
         <v>45551</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>44621</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27607,7 +27607,7 @@
         <v>44858</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27680,7 +27680,7 @@
         <v>45002</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>45470</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -27826,7 +27826,7 @@
         <v>44978</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -27899,7 +27899,7 @@
         <v>45721</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -27972,7 +27972,7 @@
         <v>45792</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28045,7 +28045,7 @@
         <v>45814</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28118,7 +28118,7 @@
         <v>45880</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28191,7 +28191,7 @@
         <v>46049</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>

--- a/Översikt MARKARYD.xlsx
+++ b/Översikt MARKARYD.xlsx
@@ -601,7 +601,7 @@
         <v>45792</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45628</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44743</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>44818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>45219</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>44818</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>44956</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>45347</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>46090</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>45453</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>45268</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>45823</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>45876</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>46203</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>44553</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>44972</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>45581</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>45762</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>44879</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>44692</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>44595</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>44700</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>44495</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>44846</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         <v>44802</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>44802</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>44802</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>44859</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>44474</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>44875</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>44638</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>44802</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         <v>44802</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>44802</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>44582</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>44848</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>44837</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>44638</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>44700</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>44539</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
         <v>44642</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>44572</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>44587</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>44508</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>44700</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>44700</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>45236</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>44760</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>45119</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>45181</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>45079</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>44581</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         <v>45524</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         <v>45265</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>44956</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>45054</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>44839</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>44601</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>45419</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>45593</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>45434</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>45600</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>45195</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>45434</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>45218</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>45539</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>45414</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>45085</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>46013</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>46013</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>46013</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>44992</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>46021</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>45582</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>44806</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>44875</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>45663</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>45329</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         <v>46034</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>45219</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         <v>45903</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>45909</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>44915</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>46042</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>44601</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>45602</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         <v>45792</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>45810</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>45700</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>45797</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>46049</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>46049</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>45195</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>45917</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>44636</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>44988</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         <v>45800</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>45800</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>45212</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>44980</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>45547</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>45426</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>44970</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>46062</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8885,7 +8885,7 @@
         <v>46063</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>44557</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>45930</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>45546</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9182,7 +9182,7 @@
         <v>46069</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>44809</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>46069</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>46069</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         <v>46069</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>46069</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9645,7 +9645,7 @@
         <v>45141</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>45942</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>45258</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>45181</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>46085</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>46085</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>46085</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
         <v>46085</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>46085</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>46090</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>45008</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         <v>46090</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>46090</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>46090</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>46090</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
         <v>46090</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10848,7 +10848,7 @@
         <v>44994</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>45191</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>44536</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>45069</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>45352</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         <v>46100</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>46100</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11359,7 +11359,7 @@
         <v>46100</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
         <v>45089</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>45216</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>44911</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11651,7 +11651,7 @@
         <v>45281</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>44644</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>45237</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>46111</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11943,7 +11943,7 @@
         <v>45512</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12016,7 +12016,7 @@
         <v>45219</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12089,7 +12089,7 @@
         <v>45556</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>45530</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12240,7 +12240,7 @@
         <v>45418</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>46129</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>46133</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
         <v>45219</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>44474</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>44798</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>45583</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12751,7 +12751,7 @@
         <v>45564</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         <v>45837</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
         <v>45063</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12970,7 +12970,7 @@
         <v>45428</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>45923</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>45281</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>45281</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>45842</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>44984</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>45842</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>45107</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13564,7 +13564,7 @@
         <v>45719</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>45666</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13710,7 +13710,7 @@
         <v>44928</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>45562</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         <v>45771</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13929,7 +13929,7 @@
         <v>44902</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>44516</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14075,7 +14075,7 @@
         <v>44677</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>44578</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14226,7 +14226,7 @@
         <v>45798</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
         <v>45670</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14372,7 +14372,7 @@
         <v>45678</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14445,7 +14445,7 @@
         <v>45678</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14518,7 +14518,7 @@
         <v>45678</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14591,7 +14591,7 @@
         <v>45161</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>45643</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>44606</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14810,7 +14810,7 @@
         <v>44911</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14883,7 +14883,7 @@
         <v>45000</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         <v>44935</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15034,7 +15034,7 @@
         <v>44935</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>45473</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
         <v>44977</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15253,7 +15253,7 @@
         <v>44977</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>45882</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>45769</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15472,7 +15472,7 @@
         <v>44887</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>45532</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>45614</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15691,7 +15691,7 @@
         <v>45225</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15764,7 +15764,7 @@
         <v>45236</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15837,7 +15837,7 @@
         <v>45258</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>44565</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15983,7 +15983,7 @@
         <v>45170</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>46149</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16129,7 +16129,7 @@
         <v>44673</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>44673</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>45769</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16348,7 +16348,7 @@
         <v>44992</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>45267</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>45265</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16567,7 +16567,7 @@
         <v>45874</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16640,7 +16640,7 @@
         <v>45265</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
         <v>45980</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16786,7 +16786,7 @@
         <v>45999</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>45203</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16932,7 +16932,7 @@
         <v>46155</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>45378</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>46141</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17151,7 +17151,7 @@
         <v>45181</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17224,7 +17224,7 @@
         <v>45837</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17297,7 +17297,7 @@
         <v>46162</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17370,7 +17370,7 @@
         <v>45547</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>44956</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>45880</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>44616</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>45209</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
         <v>44958</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>45470</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17886,7 +17886,7 @@
         <v>45880</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>46168</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18032,7 +18032,7 @@
         <v>44818</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         <v>45160</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>45092</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>45218</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18324,7 +18324,7 @@
         <v>46175</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>45678</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>45678</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18543,7 +18543,7 @@
         <v>45678</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18616,7 +18616,7 @@
         <v>45558</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>44835</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>45266</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18835,7 +18835,7 @@
         <v>45281</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18908,7 +18908,7 @@
         <v>45512</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>45428</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>45077</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19132,7 +19132,7 @@
         <v>46190</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>45075</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>45680</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
         <v>45275</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19434,7 +19434,7 @@
         <v>44823</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19507,7 +19507,7 @@
         <v>45155</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19580,7 +19580,7 @@
         <v>44999</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
         <v>44579</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19726,7 +19726,7 @@
         <v>45404</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         <v>45306</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19872,7 +19872,7 @@
         <v>45281</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19945,7 +19945,7 @@
         <v>45040</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20018,7 +20018,7 @@
         <v>45080</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20091,7 +20091,7 @@
         <v>45021</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20164,7 +20164,7 @@
         <v>46206</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20237,7 +20237,7 @@
         <v>46210</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>44992</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20388,7 +20388,7 @@
         <v>45476</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>45127</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20534,7 +20534,7 @@
         <v>46213</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20607,7 +20607,7 @@
         <v>44498</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20680,7 +20680,7 @@
         <v>45370</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20753,7 +20753,7 @@
         <v>45357</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20826,7 +20826,7 @@
         <v>45361</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20899,7 +20899,7 @@
         <v>45191</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20972,7 +20972,7 @@
         <v>45282</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21045,7 +21045,7 @@
         <v>46267</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21118,7 +21118,7 @@
         <v>45026</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21191,7 +21191,7 @@
         <v>45218</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21264,7 +21264,7 @@
         <v>46269</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21337,7 +21337,7 @@
         <v>46269</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21410,7 +21410,7 @@
         <v>45117</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>44700</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21561,7 +21561,7 @@
         <v>46269</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21634,7 +21634,7 @@
         <v>45281</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21712,7 +21712,7 @@
         <v>45240</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21785,7 +21785,7 @@
         <v>45625</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21858,7 +21858,7 @@
         <v>45196</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44902</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
         <v>46281</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22077,7 +22077,7 @@
         <v>45268</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>45296</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22228,7 +22228,7 @@
         <v>44790</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22301,7 +22301,7 @@
         <v>44587</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>45085</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22447,7 +22447,7 @@
         <v>44498</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22520,7 +22520,7 @@
         <v>46282</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22593,7 +22593,7 @@
         <v>44601</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>44601</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22749,7 +22749,7 @@
         <v>46240</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22827,7 +22827,7 @@
         <v>44572</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22900,7 +22900,7 @@
         <v>46240</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22978,7 +22978,7 @@
         <v>46282</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23051,7 +23051,7 @@
         <v>45141</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>46244</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23207,7 +23207,7 @@
         <v>45407</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23280,7 +23280,7 @@
         <v>45054</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>45069</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>45210</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>46288</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>45707</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>45282</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>46290</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23791,7 +23791,7 @@
         <v>45593</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23864,7 +23864,7 @@
         <v>44531</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23937,7 +23937,7 @@
         <v>45166</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24010,7 +24010,7 @@
         <v>45687</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24083,7 +24083,7 @@
         <v>44844</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24161,7 +24161,7 @@
         <v>45371</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24234,7 +24234,7 @@
         <v>45230</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24307,7 +24307,7 @@
         <v>45257</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24380,7 +24380,7 @@
         <v>46297</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24453,7 +24453,7 @@
         <v>45090</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24526,7 +24526,7 @@
         <v>45217</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>45372</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24672,7 +24672,7 @@
         <v>46297</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>45678</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24818,7 +24818,7 @@
         <v>46297</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24891,7 +24891,7 @@
         <v>44581</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24964,7 +24964,7 @@
         <v>44553</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25037,7 +25037,7 @@
         <v>44810</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25110,7 +25110,7 @@
         <v>45671</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         <v>45344</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25256,7 +25256,7 @@
         <v>44848</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>45678</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25402,7 +25402,7 @@
         <v>45230</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25475,7 +25475,7 @@
         <v>45258</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>45080</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25621,7 +25621,7 @@
         <v>44984</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25694,7 +25694,7 @@
         <v>45275</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>44950</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25845,7 +25845,7 @@
         <v>45681</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25918,7 +25918,7 @@
         <v>45462</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -25991,7 +25991,7 @@
         <v>45372</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26064,7 +26064,7 @@
         <v>45566</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26137,7 +26137,7 @@
         <v>45400</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26210,7 +26210,7 @@
         <v>45173</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26283,7 +26283,7 @@
         <v>45306</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26356,7 +26356,7 @@
         <v>45428</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>45628</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26502,7 +26502,7 @@
         <v>45265</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26575,7 +26575,7 @@
         <v>45230</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26648,7 +26648,7 @@
         <v>45607</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26721,7 +26721,7 @@
         <v>45581</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -26794,7 +26794,7 @@
         <v>45783</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         <v>45609</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -26940,7 +26940,7 @@
         <v>45637</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27018,7 +27018,7 @@
         <v>45637</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>45609</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>45609</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27242,7 +27242,7 @@
         <v>45444</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27315,7 +27315,7 @@
         <v>45232</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>45014</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27461,7 +27461,7 @@
         <v>45551</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>44621</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27607,7 +27607,7 @@
         <v>44858</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27680,7 +27680,7 @@
         <v>45002</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>45470</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -27826,7 +27826,7 @@
         <v>44978</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -27899,7 +27899,7 @@
         <v>45721</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -27972,7 +27972,7 @@
         <v>45792</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28045,7 +28045,7 @@
         <v>45814</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28118,7 +28118,7 @@
         <v>45880</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28191,7 +28191,7 @@
         <v>46049</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>

--- a/Översikt MARKARYD.xlsx
+++ b/Översikt MARKARYD.xlsx
@@ -601,7 +601,7 @@
         <v>45792</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45628</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44743</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>44818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>45219</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>44818</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>45453</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>45347</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>44553</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>45268</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>45823</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>44956</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>46090</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>44972</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>45581</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>45762</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>44879</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>44692</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>44595</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>44495</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>44846</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>44802</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>44802</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>44802</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>44859</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>44875</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>44638</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>44700</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>44539</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>44587</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>44802</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>44802</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44642</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>44572</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>44802</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>44582</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>44837</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>44848</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>44638</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>44508</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>45371</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>44700</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>44700</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>44823</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>45670</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>45404</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>45219</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>44902</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>45077</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>44958</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>45008</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>45217</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>44970</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>45547</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>45370</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>45428</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>45275</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         <v>45558</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>44915</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>44988</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>45344</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>45771</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>45265</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>45196</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>45054</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         <v>45512</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>44810</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>45426</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         <v>45054</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>45195</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>45378</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>45265</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>45671</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>45161</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>45155</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>45069</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>45281</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>45069</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>45546</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>45414</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>44572</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>44806</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>45210</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>45040</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         <v>44980</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         <v>44601</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>45265</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>45258</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7696,7 +7696,7 @@
         <v>45258</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         <v>45063</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>45329</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>45419</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>45275</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         <v>45218</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>44848</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>45266</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         <v>45021</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>44992</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8431,7 +8431,7 @@
         <v>45407</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>45530</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>45539</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>45352</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>44835</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>44498</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8879,7 +8879,7 @@
         <v>45085</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>45428</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>45903</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         <v>44999</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9176,7 +9176,7 @@
         <v>44579</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         <v>45524</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>45230</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>45607</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>45909</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>45306</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>45581</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>45700</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>45166</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>45810</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
         <v>44875</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9989,7 +9989,7 @@
         <v>44498</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10062,7 +10062,7 @@
         <v>45783</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10135,7 +10135,7 @@
         <v>45609</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>45609</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10281,7 +10281,7 @@
         <v>45593</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>44587</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>44636</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>45357</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>45361</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>45609</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>45637</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>45141</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10875,7 +10875,7 @@
         <v>45637</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>45556</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>45917</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11099,7 +11099,7 @@
         <v>45216</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>45444</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>45582</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11318,7 +11318,7 @@
         <v>45562</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>45600</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11464,7 +11464,7 @@
         <v>44516</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11537,7 +11537,7 @@
         <v>45547</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>45191</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>45085</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>44557</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11834,7 +11834,7 @@
         <v>45593</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11912,7 +11912,7 @@
         <v>44565</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11985,7 +11985,7 @@
         <v>45127</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12058,7 +12058,7 @@
         <v>45232</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>44950</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>45026</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         <v>45687</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12350,7 +12350,7 @@
         <v>45512</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>45792</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         <v>45930</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>44536</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>45372</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12715,7 +12715,7 @@
         <v>45583</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12788,7 +12788,7 @@
         <v>45797</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>44581</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
         <v>45230</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
         <v>45800</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13085,7 +13085,7 @@
         <v>45800</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         <v>45678</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>45678</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13304,7 +13304,7 @@
         <v>45678</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         <v>45209</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13450,7 +13450,7 @@
         <v>44984</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13523,7 +13523,7 @@
         <v>44977</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13596,7 +13596,7 @@
         <v>45089</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>45219</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13742,7 +13742,7 @@
         <v>45707</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13815,7 +13815,7 @@
         <v>45090</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>45942</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13961,7 +13961,7 @@
         <v>45434</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>45191</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>45678</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>45117</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
         <v>45282</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         <v>45434</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14404,7 +14404,7 @@
         <v>45237</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
         <v>45625</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>45141</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>44677</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>45080</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>45267</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>45258</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>44818</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>45079</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
         <v>45080</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>45181</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>44984</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>45418</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15353,7 +15353,7 @@
         <v>45181</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>45160</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>44992</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>45473</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>45681</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>45680</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>44956</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15869,7 +15869,7 @@
         <v>45678</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>45678</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16015,7 +16015,7 @@
         <v>45678</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>45400</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16161,7 +16161,7 @@
         <v>45663</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16234,7 +16234,7 @@
         <v>45181</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16312,7 +16312,7 @@
         <v>45614</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         <v>45219</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>45842</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>45842</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>45719</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>45643</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>45107</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>44798</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         <v>44790</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16974,7 +16974,7 @@
         <v>45281</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>45296</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
         <v>44977</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>45306</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17271,7 +17271,7 @@
         <v>45092</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>45257</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>45882</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>45230</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17563,7 +17563,7 @@
         <v>45476</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17636,7 +17636,7 @@
         <v>45281</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17709,7 +17709,7 @@
         <v>45769</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17782,7 +17782,7 @@
         <v>44839</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17860,7 +17860,7 @@
         <v>45240</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17933,7 +17933,7 @@
         <v>45170</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         <v>45769</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>44673</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18152,7 +18152,7 @@
         <v>44673</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         <v>45874</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18298,7 +18298,7 @@
         <v>45173</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18371,7 +18371,7 @@
         <v>45880</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18444,7 +18444,7 @@
         <v>45265</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18517,7 +18517,7 @@
         <v>45212</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18590,7 +18590,7 @@
         <v>45880</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18663,7 +18663,7 @@
         <v>45218</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>45268</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>45195</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>46100</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>46100</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>46100</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19106,7 +19106,7 @@
         <v>45203</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19179,7 +19179,7 @@
         <v>45075</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>44994</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>45236</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19403,7 +19403,7 @@
         <v>46111</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>45281</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>44844</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>45628</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>44935</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>44935</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>44553</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         <v>44911</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>45000</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20070,7 +20070,7 @@
         <v>44601</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20148,7 +20148,7 @@
         <v>44606</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20221,7 +20221,7 @@
         <v>44581</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20294,7 +20294,7 @@
         <v>44531</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20367,7 +20367,7 @@
         <v>44809</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20440,7 +20440,7 @@
         <v>45566</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20513,7 +20513,7 @@
         <v>44992</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>46133</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20659,7 +20659,7 @@
         <v>45119</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20732,7 +20732,7 @@
         <v>45281</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>45281</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20878,7 +20878,7 @@
         <v>44644</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20951,7 +20951,7 @@
         <v>45236</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21024,7 +21024,7 @@
         <v>45462</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21097,7 +21097,7 @@
         <v>44887</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21170,7 +21170,7 @@
         <v>44578</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         <v>46013</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>45837</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21394,7 +21394,7 @@
         <v>45602</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         <v>46013</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>46013</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>45428</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>46021</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>44616</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>44902</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>44760</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>45798</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>44911</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>44601</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>44601</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22285,7 +22285,7 @@
         <v>46034</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22358,7 +22358,7 @@
         <v>45666</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
         <v>44700</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22504,7 +22504,7 @@
         <v>45678</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         <v>45218</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22650,7 +22650,7 @@
         <v>45470</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22723,7 +22723,7 @@
         <v>46042</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22796,7 +22796,7 @@
         <v>45225</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22869,7 +22869,7 @@
         <v>45564</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22942,7 +22942,7 @@
         <v>45923</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>44928</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>44956</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23161,7 +23161,7 @@
         <v>45372</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
         <v>45282</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23307,7 +23307,7 @@
         <v>45532</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23380,7 +23380,7 @@
         <v>46062</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23453,7 +23453,7 @@
         <v>46063</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>46069</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>46069</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23682,7 +23682,7 @@
         <v>46069</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23760,7 +23760,7 @@
         <v>46149</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23833,7 +23833,7 @@
         <v>46069</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23911,7 +23911,7 @@
         <v>46069</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>46085</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24062,7 +24062,7 @@
         <v>46085</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>45980</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24208,7 +24208,7 @@
         <v>46085</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24281,7 +24281,7 @@
         <v>46085</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>46085</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24427,7 +24427,7 @@
         <v>45999</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24500,7 +24500,7 @@
         <v>46090</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>46090</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>46090</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>46090</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24812,7 +24812,7 @@
         <v>46090</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24890,7 +24890,7 @@
         <v>46090</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>46141</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>45837</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>46168</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>46175</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>46190</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>46213</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>46267</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25479,7 +25479,7 @@
         <v>46269</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25552,7 +25552,7 @@
         <v>46269</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>46269</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>46282</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>46240</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         <v>46282</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>46240</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>46281</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>46244</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26151,7 +26151,7 @@
         <v>46288</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26224,7 +26224,7 @@
         <v>46290</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>46155</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26370,7 +26370,7 @@
         <v>46049</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26443,7 +26443,7 @@
         <v>46297</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26516,7 +26516,7 @@
         <v>46297</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>46297</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>46210</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -26740,7 +26740,7 @@
         <v>46300</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -26818,7 +26818,7 @@
         <v>44621</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -26891,7 +26891,7 @@
         <v>45014</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -26964,7 +26964,7 @@
         <v>45551</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27037,7 +27037,7 @@
         <v>44858</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27110,7 +27110,7 @@
         <v>45002</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27183,7 +27183,7 @@
         <v>45470</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27256,7 +27256,7 @@
         <v>44978</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27329,7 +27329,7 @@
         <v>45721</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27402,7 +27402,7 @@
         <v>45792</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>45814</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         <v>45880</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27621,7 +27621,7 @@
         <v>46049</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>

--- a/Översikt MARKARYD.xlsx
+++ b/Översikt MARKARYD.xlsx
@@ -601,7 +601,7 @@
         <v>45792</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45628</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44743</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>44818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>45219</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>44818</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>45453</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>45347</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>44553</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>45268</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>45823</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>44956</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>46090</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>44972</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>45581</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>45762</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>44879</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>44692</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>44595</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>44495</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>44846</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>44802</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>44802</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>44802</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>44859</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>44875</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>44638</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>44700</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>44539</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>44587</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>44802</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>44802</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44642</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>44572</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>44802</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>44582</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>44837</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>44848</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>44638</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>44508</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>45371</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>44700</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>44700</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>44823</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>45670</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>45404</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>45219</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>44902</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>45077</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>44958</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>45008</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>45217</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>44970</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>45547</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>45370</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>45428</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>45275</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         <v>45558</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>44915</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>44988</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>45344</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>45771</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>45265</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>45196</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>45054</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         <v>45512</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>44810</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>45426</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         <v>45054</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>45195</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>45378</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
         <v>45265</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
         <v>45671</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>45161</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>45155</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>45069</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>45281</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>45069</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>45546</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>45414</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>44572</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>44806</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>45210</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>45040</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         <v>44980</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         <v>44601</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>45265</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>45258</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7696,7 +7696,7 @@
         <v>45258</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         <v>45063</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>45329</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>45419</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>45275</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         <v>45218</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>44848</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>45266</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         <v>45021</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>44992</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8431,7 +8431,7 @@
         <v>45407</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>45530</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>45539</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>45352</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>44835</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>44498</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8879,7 +8879,7 @@
         <v>45085</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>45428</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>45903</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         <v>44999</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9176,7 +9176,7 @@
         <v>44579</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         <v>45524</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>45230</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>45607</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>45909</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>45306</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>45581</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>45700</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>45166</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>45810</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
         <v>44875</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9989,7 +9989,7 @@
         <v>44498</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10062,7 +10062,7 @@
         <v>45783</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10135,7 +10135,7 @@
         <v>45609</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>45609</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10281,7 +10281,7 @@
         <v>45593</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>44587</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>44636</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>45357</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>45361</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>45609</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>45637</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>45141</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10875,7 +10875,7 @@
         <v>45637</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>45556</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>45917</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11099,7 +11099,7 @@
         <v>45216</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>45444</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>45582</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11318,7 +11318,7 @@
         <v>45562</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>45600</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11464,7 +11464,7 @@
         <v>44516</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11537,7 +11537,7 @@
         <v>45547</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>45191</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>45085</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>44557</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11834,7 +11834,7 @@
         <v>45593</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11912,7 +11912,7 @@
         <v>44565</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11985,7 +11985,7 @@
         <v>45127</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12058,7 +12058,7 @@
         <v>45232</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>44950</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12204,7 +12204,7 @@
         <v>45026</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         <v>45687</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12350,7 +12350,7 @@
         <v>45512</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>45792</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         <v>45930</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>44536</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>45372</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12715,7 +12715,7 @@
         <v>45583</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12788,7 +12788,7 @@
         <v>45797</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>44581</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
         <v>45230</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
         <v>45800</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13085,7 +13085,7 @@
         <v>45800</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         <v>45678</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>45678</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13304,7 +13304,7 @@
         <v>45678</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         <v>45209</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13450,7 +13450,7 @@
         <v>44984</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13523,7 +13523,7 @@
         <v>44977</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13596,7 +13596,7 @@
         <v>45089</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>45219</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13742,7 +13742,7 @@
         <v>45707</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13815,7 +13815,7 @@
         <v>45090</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>45942</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13961,7 +13961,7 @@
         <v>45434</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>45191</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>45678</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>45117</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
         <v>45282</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         <v>45434</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14404,7 +14404,7 @@
         <v>45237</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
         <v>45625</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>45141</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14623,7 +14623,7 @@
         <v>44677</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>45080</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14769,7 +14769,7 @@
         <v>45267</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>45258</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>44818</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>45079</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
         <v>45080</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15134,7 +15134,7 @@
         <v>45181</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15207,7 +15207,7 @@
         <v>44984</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>45418</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15353,7 +15353,7 @@
         <v>45181</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>45160</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>44992</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>45473</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>45681</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>45680</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>44956</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15869,7 +15869,7 @@
         <v>45678</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>45678</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16015,7 +16015,7 @@
         <v>45678</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>45400</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16161,7 +16161,7 @@
         <v>45663</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16234,7 +16234,7 @@
         <v>45181</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16312,7 +16312,7 @@
         <v>45614</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         <v>45219</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>45842</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>45842</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>45719</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>45643</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>45107</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>44798</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         <v>44790</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16974,7 +16974,7 @@
         <v>45281</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>45296</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
         <v>44977</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>45306</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17271,7 +17271,7 @@
         <v>45092</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>45257</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>45882</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>45230</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17563,7 +17563,7 @@
         <v>45476</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17636,7 +17636,7 @@
         <v>45281</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17709,7 +17709,7 @@
         <v>45769</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17782,7 +17782,7 @@
         <v>44839</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17860,7 +17860,7 @@
         <v>45240</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17933,7 +17933,7 @@
         <v>45170</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         <v>45769</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>44673</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18152,7 +18152,7 @@
         <v>44673</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         <v>45874</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18298,7 +18298,7 @@
         <v>45173</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18371,7 +18371,7 @@
         <v>45880</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18444,7 +18444,7 @@
         <v>45265</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18517,7 +18517,7 @@
         <v>45212</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18590,7 +18590,7 @@
         <v>45880</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18663,7 +18663,7 @@
         <v>45218</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>45268</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18814,7 +18814,7 @@
         <v>45195</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>46100</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>46100</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19033,7 +19033,7 @@
         <v>46100</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19106,7 +19106,7 @@
         <v>45203</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19179,7 +19179,7 @@
         <v>45075</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>44994</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>45236</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19403,7 +19403,7 @@
         <v>46111</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>45281</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>44844</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>45628</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>44935</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>44935</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>44553</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         <v>44911</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>45000</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20070,7 +20070,7 @@
         <v>44601</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20148,7 +20148,7 @@
         <v>44606</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20221,7 +20221,7 @@
         <v>44581</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20294,7 +20294,7 @@
         <v>44531</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20367,7 +20367,7 @@
         <v>44809</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20440,7 +20440,7 @@
         <v>45566</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20513,7 +20513,7 @@
         <v>44992</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>46133</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20659,7 +20659,7 @@
         <v>45119</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20732,7 +20732,7 @@
         <v>45281</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20805,7 +20805,7 @@
         <v>45281</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20878,7 +20878,7 @@
         <v>44644</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20951,7 +20951,7 @@
         <v>45236</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21024,7 +21024,7 @@
         <v>45462</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21097,7 +21097,7 @@
         <v>44887</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21170,7 +21170,7 @@
         <v>44578</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         <v>46013</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>45837</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21394,7 +21394,7 @@
         <v>45602</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         <v>46013</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>46013</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>45428</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>46021</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>44616</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>44902</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>44760</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>45798</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>44911</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>44601</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>44601</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22285,7 +22285,7 @@
         <v>46034</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22358,7 +22358,7 @@
         <v>45666</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
         <v>44700</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22504,7 +22504,7 @@
         <v>45678</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         <v>45218</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22650,7 +22650,7 @@
         <v>45470</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22723,7 +22723,7 @@
         <v>46042</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22796,7 +22796,7 @@
         <v>45225</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22869,7 +22869,7 @@
         <v>45564</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22942,7 +22942,7 @@
         <v>45923</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>44928</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>44956</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23161,7 +23161,7 @@
         <v>45372</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
         <v>45282</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23307,7 +23307,7 @@
         <v>45532</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23380,7 +23380,7 @@
         <v>46062</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23453,7 +23453,7 @@
         <v>46063</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>46069</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>46069</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23682,7 +23682,7 @@
         <v>46069</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23760,7 +23760,7 @@
         <v>46149</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23833,7 +23833,7 @@
         <v>46069</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23911,7 +23911,7 @@
         <v>46069</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>46085</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24062,7 +24062,7 @@
         <v>46085</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>45980</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24208,7 +24208,7 @@
         <v>46085</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24281,7 +24281,7 @@
         <v>46085</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>46085</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24427,7 +24427,7 @@
         <v>45999</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24500,7 +24500,7 @@
         <v>46090</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>46090</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>46090</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>46090</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24812,7 +24812,7 @@
         <v>46090</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24890,7 +24890,7 @@
         <v>46090</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>46141</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>45837</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>46168</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>46175</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>46190</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>46213</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>46267</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25479,7 +25479,7 @@
         <v>46269</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25552,7 +25552,7 @@
         <v>46269</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>46269</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>46282</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>46240</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         <v>46282</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>46240</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>46281</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>46244</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26151,7 +26151,7 @@
         <v>46288</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26224,7 +26224,7 @@
         <v>46290</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>46155</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26370,7 +26370,7 @@
         <v>46049</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26443,7 +26443,7 @@
         <v>46297</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26516,7 +26516,7 @@
         <v>46297</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>46297</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>46210</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -26740,7 +26740,7 @@
         <v>46300</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -26818,7 +26818,7 @@
         <v>44621</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -26891,7 +26891,7 @@
         <v>45014</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -26964,7 +26964,7 @@
         <v>45551</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27037,7 +27037,7 @@
         <v>44858</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27110,7 +27110,7 @@
         <v>45002</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27183,7 +27183,7 @@
         <v>45470</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27256,7 +27256,7 @@
         <v>44978</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27329,7 +27329,7 @@
         <v>45721</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27402,7 +27402,7 @@
         <v>45792</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>45814</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         <v>45880</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27621,7 +27621,7 @@
         <v>46049</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>

--- a/Översikt MARKARYD.xlsx
+++ b/Översikt MARKARYD.xlsx
@@ -601,7 +601,7 @@
         <v>45792</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45628</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44743</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>44818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>45219</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>44818</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>44956</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>45347</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>45453</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>45268</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>46090</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>44553</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>45823</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>44972</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>45581</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>45762</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>44879</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>44692</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>44595</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>44495</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>44846</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>44802</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>44802</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>44802</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>44859</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>44875</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>44638</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>44802</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>44802</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>44802</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>44582</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>44848</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44837</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>44638</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>44700</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>44539</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>44587</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>44572</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>44642</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>44508</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>44700</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>44700</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>45236</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>44760</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>45079</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>45181</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>44581</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>45119</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>45265</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>45524</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         <v>45054</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>44956</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>44839</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>44601</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
         <v>45419</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>45434</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>45434</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>45539</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>45085</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         <v>45414</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>44992</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>45195</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         <v>44806</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>45663</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>45582</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>44875</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6095,7 +6095,7 @@
         <v>45329</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>45219</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>44601</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         <v>45602</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         <v>44915</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         <v>45195</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>44636</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         <v>44988</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>45212</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>44980</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>45426</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>44970</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         <v>45547</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>44809</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
         <v>45141</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7200,7 +7200,7 @@
         <v>44557</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>45258</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>45181</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>45008</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>44994</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>44536</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>45352</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         <v>45191</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>45069</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         <v>45089</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>45216</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         <v>45281</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>44911</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>44644</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>45546</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>45218</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>45512</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         <v>45666</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>45219</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         <v>45556</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8670,7 +8670,7 @@
         <v>45798</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         <v>45530</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         <v>45219</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>45218</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>44798</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9040,7 +9040,7 @@
         <v>45583</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9113,7 +9113,7 @@
         <v>45903</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>45909</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>45532</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>45810</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         <v>45700</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         <v>45063</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>45428</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>45281</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>45281</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>45917</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>44984</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>44928</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>45562</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>45771</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10145,7 +10145,7 @@
         <v>44902</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>44516</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10291,7 +10291,7 @@
         <v>44677</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10364,7 +10364,7 @@
         <v>46149</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10437,7 +10437,7 @@
         <v>45930</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>44578</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>45942</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10661,7 +10661,7 @@
         <v>45670</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>45678</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         <v>45678</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>45678</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>45161</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>45980</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11099,7 +11099,7 @@
         <v>45643</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>45999</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>44606</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11318,7 +11318,7 @@
         <v>44911</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>45000</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>44935</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
         <v>44935</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>45473</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>44977</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>44977</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11834,7 +11834,7 @@
         <v>44887</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>46141</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11980,7 +11980,7 @@
         <v>45837</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>45614</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>45225</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
         <v>45236</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>45258</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12345,7 +12345,7 @@
         <v>44565</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
         <v>44992</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12491,7 +12491,7 @@
         <v>45267</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12564,7 +12564,7 @@
         <v>45265</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12637,7 +12637,7 @@
         <v>45265</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12710,7 +12710,7 @@
         <v>45203</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12783,7 +12783,7 @@
         <v>45378</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12856,7 +12856,7 @@
         <v>45181</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12929,7 +12929,7 @@
         <v>45547</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         <v>44956</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
         <v>46168</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13153,7 +13153,7 @@
         <v>44616</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>45209</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13299,7 +13299,7 @@
         <v>44958</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13372,7 +13372,7 @@
         <v>45470</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
         <v>44818</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>45160</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
         <v>45092</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13664,7 +13664,7 @@
         <v>46013</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>46013</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>46013</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>46021</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>45678</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>45678</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>45678</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>45558</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14248,7 +14248,7 @@
         <v>44835</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>45266</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14394,7 +14394,7 @@
         <v>45281</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14467,7 +14467,7 @@
         <v>45512</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>45428</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14618,7 +14618,7 @@
         <v>46034</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14691,7 +14691,7 @@
         <v>45077</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>46175</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>46042</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>45075</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>45680</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
         <v>45275</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>44823</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>45155</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>44999</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>46062</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>44579</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>46063</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>45404</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>45306</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>45281</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>46069</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>45040</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>46069</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>46069</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>46069</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16181,7 +16181,7 @@
         <v>46069</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>45080</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16332,7 +16332,7 @@
         <v>45021</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16405,7 +16405,7 @@
         <v>46190</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>46085</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>46085</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16624,7 +16624,7 @@
         <v>46085</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16697,7 +16697,7 @@
         <v>46085</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>46085</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>46090</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>46090</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>46090</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17077,7 +17077,7 @@
         <v>46090</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17155,7 +17155,7 @@
         <v>46090</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>46090</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17311,7 +17311,7 @@
         <v>44992</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17384,7 +17384,7 @@
         <v>45476</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17457,7 +17457,7 @@
         <v>46100</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         <v>45127</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17603,7 +17603,7 @@
         <v>46100</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17676,7 +17676,7 @@
         <v>46100</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17749,7 +17749,7 @@
         <v>44498</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
         <v>45370</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>46111</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17968,7 +17968,7 @@
         <v>45357</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18041,7 +18041,7 @@
         <v>45361</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18114,7 +18114,7 @@
         <v>45191</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18187,7 +18187,7 @@
         <v>45282</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18260,7 +18260,7 @@
         <v>45026</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         <v>45218</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>45117</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18484,7 +18484,7 @@
         <v>44700</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18557,7 +18557,7 @@
         <v>45281</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18635,7 +18635,7 @@
         <v>45240</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>46133</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18781,7 +18781,7 @@
         <v>45625</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18854,7 +18854,7 @@
         <v>45564</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18927,7 +18927,7 @@
         <v>45196</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19000,7 +19000,7 @@
         <v>44902</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19073,7 +19073,7 @@
         <v>45837</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>45268</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19224,7 +19224,7 @@
         <v>45923</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19297,7 +19297,7 @@
         <v>45296</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>44790</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19443,7 +19443,7 @@
         <v>44587</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19516,7 +19516,7 @@
         <v>45085</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>44498</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>44601</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
         <v>44601</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19818,7 +19818,7 @@
         <v>44572</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19891,7 +19891,7 @@
         <v>45141</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>46213</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>45407</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20115,7 +20115,7 @@
         <v>45054</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>45069</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>45210</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20334,7 +20334,7 @@
         <v>45707</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20407,7 +20407,7 @@
         <v>45282</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20480,7 +20480,7 @@
         <v>45593</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20553,7 +20553,7 @@
         <v>44531</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         <v>45166</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>45687</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>44844</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20850,7 +20850,7 @@
         <v>45371</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20923,7 +20923,7 @@
         <v>45230</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>45257</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>45090</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21142,7 +21142,7 @@
         <v>46281</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21215,7 +21215,7 @@
         <v>45217</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21288,7 +21288,7 @@
         <v>46282</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21361,7 +21361,7 @@
         <v>46240</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21439,7 +21439,7 @@
         <v>45372</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>46240</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21590,7 +21590,7 @@
         <v>46282</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>45678</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>44581</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21809,7 +21809,7 @@
         <v>44553</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21882,7 +21882,7 @@
         <v>44810</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         <v>45671</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22028,7 +22028,7 @@
         <v>46244</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22106,7 +22106,7 @@
         <v>45344</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22179,7 +22179,7 @@
         <v>44848</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22252,7 +22252,7 @@
         <v>45678</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22325,7 +22325,7 @@
         <v>45230</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22398,7 +22398,7 @@
         <v>46288</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22471,7 +22471,7 @@
         <v>45258</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22544,7 +22544,7 @@
         <v>45080</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22617,7 +22617,7 @@
         <v>44984</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22690,7 +22690,7 @@
         <v>46290</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22763,7 +22763,7 @@
         <v>45275</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22841,7 +22841,7 @@
         <v>44950</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22914,7 +22914,7 @@
         <v>45681</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22987,7 +22987,7 @@
         <v>45462</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23060,7 +23060,7 @@
         <v>45372</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23133,7 +23133,7 @@
         <v>45566</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23206,7 +23206,7 @@
         <v>45400</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>45173</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>45306</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23425,7 +23425,7 @@
         <v>45428</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23498,7 +23498,7 @@
         <v>46297</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
         <v>45628</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
         <v>45265</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>46297</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23790,7 +23790,7 @@
         <v>46297</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23863,7 +23863,7 @@
         <v>46049</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23936,7 +23936,7 @@
         <v>45230</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24009,7 +24009,7 @@
         <v>45607</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24082,7 +24082,7 @@
         <v>46210</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>45581</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24233,7 +24233,7 @@
         <v>45783</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24306,7 +24306,7 @@
         <v>46155</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24379,7 +24379,7 @@
         <v>45609</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24452,7 +24452,7 @@
         <v>45637</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24530,7 +24530,7 @@
         <v>45637</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24608,7 +24608,7 @@
         <v>46300</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>45609</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>45609</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>45444</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24905,7 +24905,7 @@
         <v>45232</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>45593</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25056,7 +25056,7 @@
         <v>45600</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25129,7 +25129,7 @@
         <v>45792</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25202,7 +25202,7 @@
         <v>45797</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25280,7 +25280,7 @@
         <v>45800</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25353,7 +25353,7 @@
         <v>45800</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>46269</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25499,7 +25499,7 @@
         <v>46267</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
         <v>45237</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>46269</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25718,7 +25718,7 @@
         <v>46269</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25791,7 +25791,7 @@
         <v>45418</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>45842</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>45842</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>45107</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26088,7 +26088,7 @@
         <v>45719</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26161,7 +26161,7 @@
         <v>45882</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26234,7 +26234,7 @@
         <v>45769</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26307,7 +26307,7 @@
         <v>45170</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26380,7 +26380,7 @@
         <v>44673</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>44673</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26526,7 +26526,7 @@
         <v>45769</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26599,7 +26599,7 @@
         <v>45874</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>45880</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -26745,7 +26745,7 @@
         <v>45880</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -26818,7 +26818,7 @@
         <v>45014</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -26891,7 +26891,7 @@
         <v>45551</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -26964,7 +26964,7 @@
         <v>44621</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27037,7 +27037,7 @@
         <v>44858</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27110,7 +27110,7 @@
         <v>45002</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27183,7 +27183,7 @@
         <v>45470</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27256,7 +27256,7 @@
         <v>44978</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27329,7 +27329,7 @@
         <v>45721</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27402,7 +27402,7 @@
         <v>45792</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>45814</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         <v>45880</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27621,7 +27621,7 @@
         <v>46049</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>

--- a/Översikt MARKARYD.xlsx
+++ b/Översikt MARKARYD.xlsx
@@ -601,7 +601,7 @@
         <v>45792</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45628</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44743</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>44818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>45219</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>44818</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>44956</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>45347</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>45453</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>45268</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>46090</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>44553</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>45823</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>44972</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>45581</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>45762</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>44879</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>44692</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>44595</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>44495</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>44846</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>44802</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>44802</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>44802</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>44859</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>44875</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>44638</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>44802</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>44802</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>44802</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>44582</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>44848</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44837</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>44638</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>44700</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>44539</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>44587</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>44572</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>44642</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>44508</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>44700</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>44700</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>45236</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>44760</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>45079</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>45181</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>44581</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>45119</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>45265</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>45524</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         <v>45054</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>44956</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>44839</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>44601</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
         <v>45419</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>45434</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>45434</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>45539</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5511,7 +5511,7 @@
         <v>45085</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         <v>45414</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>44992</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>45195</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         <v>44806</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>45663</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>45582</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>44875</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6095,7 +6095,7 @@
         <v>45329</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>45219</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>44601</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         <v>45602</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         <v>44915</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         <v>45195</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>44636</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         <v>44988</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>45212</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>44980</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>45426</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>44970</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         <v>45547</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>44809</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
         <v>45141</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7200,7 +7200,7 @@
         <v>44557</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>45258</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>45181</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>45008</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>44994</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>44536</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         <v>45352</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         <v>45191</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         <v>45069</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         <v>45089</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>45216</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         <v>45281</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>44911</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>44644</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>45546</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>45218</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>45512</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         <v>45666</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>45219</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         <v>45556</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8670,7 +8670,7 @@
         <v>45798</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         <v>45530</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         <v>45219</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>45218</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>44798</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9040,7 +9040,7 @@
         <v>45583</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9113,7 +9113,7 @@
         <v>45903</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>45909</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>45532</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>45810</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         <v>45700</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         <v>45063</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>45428</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>45281</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>45281</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>45917</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>44984</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>44928</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>45562</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>45771</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10145,7 +10145,7 @@
         <v>44902</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>44516</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10291,7 +10291,7 @@
         <v>44677</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10364,7 +10364,7 @@
         <v>46149</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10437,7 +10437,7 @@
         <v>45930</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>44578</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>45942</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10661,7 +10661,7 @@
         <v>45670</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>45678</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         <v>45678</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>45678</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>45161</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>45980</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11099,7 +11099,7 @@
         <v>45643</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>45999</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>44606</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11318,7 +11318,7 @@
         <v>44911</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>45000</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>44935</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
         <v>44935</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>45473</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>44977</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>44977</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11834,7 +11834,7 @@
         <v>44887</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>46141</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11980,7 +11980,7 @@
         <v>45837</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>45614</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>45225</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
         <v>45236</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>45258</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12345,7 +12345,7 @@
         <v>44565</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
         <v>44992</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12491,7 +12491,7 @@
         <v>45267</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12564,7 +12564,7 @@
         <v>45265</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12637,7 +12637,7 @@
         <v>45265</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12710,7 +12710,7 @@
         <v>45203</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12783,7 +12783,7 @@
         <v>45378</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12856,7 +12856,7 @@
         <v>45181</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12929,7 +12929,7 @@
         <v>45547</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13007,7 +13007,7 @@
         <v>44956</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
         <v>46168</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13153,7 +13153,7 @@
         <v>44616</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>45209</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13299,7 +13299,7 @@
         <v>44958</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13372,7 +13372,7 @@
         <v>45470</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
         <v>44818</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>45160</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
         <v>45092</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13664,7 +13664,7 @@
         <v>46013</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>46013</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>46013</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>46021</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>45678</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>45678</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>45678</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>45558</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14248,7 +14248,7 @@
         <v>44835</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>45266</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14394,7 +14394,7 @@
         <v>45281</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14467,7 +14467,7 @@
         <v>45512</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>45428</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14618,7 +14618,7 @@
         <v>46034</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14691,7 +14691,7 @@
         <v>45077</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>46175</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>46042</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>45075</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14988,7 +14988,7 @@
         <v>45680</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
         <v>45275</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>44823</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>45155</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>44999</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>46062</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>44579</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>46063</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>45404</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>45306</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15723,7 +15723,7 @@
         <v>45281</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15796,7 +15796,7 @@
         <v>46069</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>45040</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>46069</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>46069</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>46069</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16181,7 +16181,7 @@
         <v>46069</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>45080</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16332,7 +16332,7 @@
         <v>45021</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16405,7 +16405,7 @@
         <v>46190</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>46085</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>46085</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16624,7 +16624,7 @@
         <v>46085</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16697,7 +16697,7 @@
         <v>46085</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>46085</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>46090</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>46090</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>46090</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17077,7 +17077,7 @@
         <v>46090</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17155,7 +17155,7 @@
         <v>46090</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>46090</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17311,7 +17311,7 @@
         <v>44992</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17384,7 +17384,7 @@
         <v>45476</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17457,7 +17457,7 @@
         <v>46100</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         <v>45127</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17603,7 +17603,7 @@
         <v>46100</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17676,7 +17676,7 @@
         <v>46100</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17749,7 +17749,7 @@
         <v>44498</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
         <v>45370</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>46111</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17968,7 +17968,7 @@
         <v>45357</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18041,7 +18041,7 @@
         <v>45361</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18114,7 +18114,7 @@
         <v>45191</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18187,7 +18187,7 @@
         <v>45282</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18260,7 +18260,7 @@
         <v>45026</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         <v>45218</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>45117</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18484,7 +18484,7 @@
         <v>44700</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18557,7 +18557,7 @@
         <v>45281</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18635,7 +18635,7 @@
         <v>45240</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>46133</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18781,7 +18781,7 @@
         <v>45625</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18854,7 +18854,7 @@
         <v>45564</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18927,7 +18927,7 @@
         <v>45196</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19000,7 +19000,7 @@
         <v>44902</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19073,7 +19073,7 @@
         <v>45837</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>45268</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19224,7 +19224,7 @@
         <v>45923</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19297,7 +19297,7 @@
         <v>45296</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>44790</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19443,7 +19443,7 @@
         <v>44587</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19516,7 +19516,7 @@
         <v>45085</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>44498</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>44601</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
         <v>44601</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19818,7 +19818,7 @@
         <v>44572</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19891,7 +19891,7 @@
         <v>45141</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>46213</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>45407</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20115,7 +20115,7 @@
         <v>45054</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>45069</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>45210</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20334,7 +20334,7 @@
         <v>45707</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20407,7 +20407,7 @@
         <v>45282</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20480,7 +20480,7 @@
         <v>45593</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20553,7 +20553,7 @@
         <v>44531</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         <v>45166</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>45687</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>44844</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20850,7 +20850,7 @@
         <v>45371</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20923,7 +20923,7 @@
         <v>45230</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>45257</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>45090</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21142,7 +21142,7 @@
         <v>46281</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21215,7 +21215,7 @@
         <v>45217</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21288,7 +21288,7 @@
         <v>46282</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21361,7 +21361,7 @@
         <v>46240</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21439,7 +21439,7 @@
         <v>45372</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>46240</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21590,7 +21590,7 @@
         <v>46282</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>45678</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>44581</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21809,7 +21809,7 @@
         <v>44553</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21882,7 +21882,7 @@
         <v>44810</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         <v>45671</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22028,7 +22028,7 @@
         <v>46244</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22106,7 +22106,7 @@
         <v>45344</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22179,7 +22179,7 @@
         <v>44848</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22252,7 +22252,7 @@
         <v>45678</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22325,7 +22325,7 @@
         <v>45230</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22398,7 +22398,7 @@
         <v>46288</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22471,7 +22471,7 @@
         <v>45258</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22544,7 +22544,7 @@
         <v>45080</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22617,7 +22617,7 @@
         <v>44984</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22690,7 +22690,7 @@
         <v>46290</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22763,7 +22763,7 @@
         <v>45275</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22841,7 +22841,7 @@
         <v>44950</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22914,7 +22914,7 @@
         <v>45681</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22987,7 +22987,7 @@
         <v>45462</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23060,7 +23060,7 @@
         <v>45372</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23133,7 +23133,7 @@
         <v>45566</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23206,7 +23206,7 @@
         <v>45400</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>45173</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>45306</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23425,7 +23425,7 @@
         <v>45428</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23498,7 +23498,7 @@
         <v>46297</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
         <v>45628</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
         <v>45265</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>46297</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23790,7 +23790,7 @@
         <v>46297</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23863,7 +23863,7 @@
         <v>46049</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23936,7 +23936,7 @@
         <v>45230</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24009,7 +24009,7 @@
         <v>45607</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24082,7 +24082,7 @@
         <v>46210</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>45581</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24233,7 +24233,7 @@
         <v>45783</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24306,7 +24306,7 @@
         <v>46155</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24379,7 +24379,7 @@
         <v>45609</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24452,7 +24452,7 @@
         <v>45637</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24530,7 +24530,7 @@
         <v>45637</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24608,7 +24608,7 @@
         <v>46300</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>45609</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>45609</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>45444</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24905,7 +24905,7 @@
         <v>45232</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>45593</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25056,7 +25056,7 @@
         <v>45600</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25129,7 +25129,7 @@
         <v>45792</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25202,7 +25202,7 @@
         <v>45797</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25280,7 +25280,7 @@
         <v>45800</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25353,7 +25353,7 @@
         <v>45800</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>46269</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25499,7 +25499,7 @@
         <v>46267</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
         <v>45237</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>46269</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25718,7 +25718,7 @@
         <v>46269</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25791,7 +25791,7 @@
         <v>45418</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>45842</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>45842</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26010,7 +26010,7 @@
         <v>45107</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26088,7 +26088,7 @@
         <v>45719</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26161,7 +26161,7 @@
         <v>45882</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26234,7 +26234,7 @@
         <v>45769</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26307,7 +26307,7 @@
         <v>45170</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26380,7 +26380,7 @@
         <v>44673</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>44673</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26526,7 +26526,7 @@
         <v>45769</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26599,7 +26599,7 @@
         <v>45874</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>45880</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -26745,7 +26745,7 @@
         <v>45880</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -26818,7 +26818,7 @@
         <v>45014</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -26891,7 +26891,7 @@
         <v>45551</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -26964,7 +26964,7 @@
         <v>44621</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27037,7 +27037,7 @@
         <v>44858</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27110,7 +27110,7 @@
         <v>45002</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27183,7 +27183,7 @@
         <v>45470</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27256,7 +27256,7 @@
         <v>44978</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27329,7 +27329,7 @@
         <v>45721</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27402,7 +27402,7 @@
         <v>45792</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>45814</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         <v>45880</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27621,7 +27621,7 @@
         <v>46049</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>

--- a/Översikt MARKARYD.xlsx
+++ b/Översikt MARKARYD.xlsx
@@ -601,7 +601,7 @@
         <v>45792</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45628</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44743</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>44818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>45219</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>44818</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>44956</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>45453</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>46090</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>45823</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>44553</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>45268</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>45347</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>44972</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>45581</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>45762</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>44879</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>44692</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>44595</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>44495</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>44846</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>44802</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>44802</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>44802</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>44859</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>44875</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>44638</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>44802</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>44802</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>44582</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>44802</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>44848</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44837</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>44638</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>44700</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>44539</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>44587</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>44642</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>44572</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>44508</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>45119</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>44700</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>44700</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>45281</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>45281</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>45218</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>45008</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>45275</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>44988</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>45771</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>45196</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>45054</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>45512</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>44810</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>44644</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>45236</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>45462</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>44887</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>44578</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>45069</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>45546</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>45414</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         <v>45602</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>45428</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>45371</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>44616</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>44823</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>45903</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>44902</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         <v>44760</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>45909</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>46141</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>45837</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>45700</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>45810</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>44911</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>44601</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>44601</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>45917</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>44700</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
         <v>46168</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7200,7 +7200,7 @@
         <v>45678</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>45218</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>45470</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7419,7 +7419,7 @@
         <v>45225</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>45930</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7565,7 +7565,7 @@
         <v>45219</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>44928</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>44956</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>45372</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         <v>45282</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7930,7 +7930,7 @@
         <v>46175</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
         <v>45217</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>45370</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
         <v>45428</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>45942</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>45426</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         <v>45404</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>45378</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>45265</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         <v>44958</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>45547</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>45195</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>45671</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>45155</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         <v>46190</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>45210</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         <v>44980</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9176,7 +9176,7 @@
         <v>44601</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>45407</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>45352</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>44806</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>46213</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>45040</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>45428</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>44999</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>45230</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>45607</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
         <v>45581</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9989,7 +9989,7 @@
         <v>45783</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10062,7 +10062,7 @@
         <v>45609</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10135,7 +10135,7 @@
         <v>45609</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>45609</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10281,7 +10281,7 @@
         <v>45637</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
         <v>45637</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10437,7 +10437,7 @@
         <v>45265</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>45444</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10583,7 +10583,7 @@
         <v>46013</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>46013</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10729,7 +10729,7 @@
         <v>46013</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10802,7 +10802,7 @@
         <v>45600</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10875,7 +10875,7 @@
         <v>46282</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>46240</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>46021</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11099,7 +11099,7 @@
         <v>46282</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>45593</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
         <v>46240</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         <v>45232</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11401,7 +11401,7 @@
         <v>46281</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>46244</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         <v>46034</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11625,7 +11625,7 @@
         <v>45792</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>45419</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>45275</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>45797</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>46042</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>46288</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>45800</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>45800</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>46290</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>46062</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>46063</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>45237</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>46069</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>46069</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>46069</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>46069</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
         <v>46069</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>44848</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12974,7 +12974,7 @@
         <v>45266</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>46085</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>46085</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         <v>46155</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>46085</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13339,7 +13339,7 @@
         <v>45418</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>46085</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>46085</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>46049</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
         <v>46090</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>46090</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>46090</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>46090</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13943,7 +13943,7 @@
         <v>46090</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14021,7 +14021,7 @@
         <v>46090</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>46297</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>46297</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>45842</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>45842</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>45719</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>46297</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>46100</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         <v>45107</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14688,7 +14688,7 @@
         <v>46210</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>46100</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>46100</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>46300</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>46111</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         <v>45530</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15141,7 +15141,7 @@
         <v>45539</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>44835</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         <v>44498</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>45882</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15438,7 +15438,7 @@
         <v>45769</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15511,7 +15511,7 @@
         <v>45170</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>45769</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>44673</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15730,7 +15730,7 @@
         <v>44673</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
         <v>45874</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15876,7 +15876,7 @@
         <v>45085</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15949,7 +15949,7 @@
         <v>45880</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16022,7 +16022,7 @@
         <v>45880</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>45218</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16168,7 +16168,7 @@
         <v>44579</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16241,7 +16241,7 @@
         <v>46133</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16314,7 +16314,7 @@
         <v>44875</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>44498</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16460,7 +16460,7 @@
         <v>44587</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
         <v>45357</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16606,7 +16606,7 @@
         <v>45361</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         <v>45556</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16752,7 +16752,7 @@
         <v>45216</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
         <v>45837</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16898,7 +16898,7 @@
         <v>46267</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>45562</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>45798</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>46269</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>46269</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>44557</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17336,7 +17336,7 @@
         <v>44565</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
         <v>46269</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>45127</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>45666</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         <v>44950</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>45026</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>45687</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>45564</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>45923</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>45372</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>45583</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>45532</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18212,7 +18212,7 @@
         <v>45678</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>45678</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18358,7 +18358,7 @@
         <v>45678</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>46317</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>45209</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>44984</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18650,7 +18650,7 @@
         <v>44977</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18723,7 +18723,7 @@
         <v>46149</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18796,7 +18796,7 @@
         <v>45089</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18869,7 +18869,7 @@
         <v>45219</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18942,7 +18942,7 @@
         <v>45707</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19015,7 +19015,7 @@
         <v>45434</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19088,7 +19088,7 @@
         <v>45980</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19161,7 +19161,7 @@
         <v>45282</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         <v>45999</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19307,7 +19307,7 @@
         <v>45267</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>45258</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19453,7 +19453,7 @@
         <v>45079</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19526,7 +19526,7 @@
         <v>45080</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>44984</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19672,7 +19672,7 @@
         <v>44992</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19745,7 +19745,7 @@
         <v>45473</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19818,7 +19818,7 @@
         <v>45680</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19891,7 +19891,7 @@
         <v>44956</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>45678</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20037,7 +20037,7 @@
         <v>45678</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20110,7 +20110,7 @@
         <v>45678</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20183,7 +20183,7 @@
         <v>45663</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20256,7 +20256,7 @@
         <v>45614</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20329,7 +20329,7 @@
         <v>44798</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20402,7 +20402,7 @@
         <v>44977</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20475,7 +20475,7 @@
         <v>45092</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20548,7 +20548,7 @@
         <v>45476</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20621,7 +20621,7 @@
         <v>44839</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>45212</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>45203</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>45075</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20923,7 +20923,7 @@
         <v>44994</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>45281</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>44844</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>45670</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21220,7 +21220,7 @@
         <v>44902</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21293,7 +21293,7 @@
         <v>45077</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>44970</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21439,7 +21439,7 @@
         <v>45558</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>44915</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21585,7 +21585,7 @@
         <v>45344</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>45265</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
         <v>45054</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>45161</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21877,7 +21877,7 @@
         <v>45069</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>45281</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>44572</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22096,7 +22096,7 @@
         <v>45258</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22169,7 +22169,7 @@
         <v>45258</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>45063</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
         <v>45329</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>45021</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>44992</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22534,7 +22534,7 @@
         <v>45524</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22612,7 +22612,7 @@
         <v>45306</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22685,7 +22685,7 @@
         <v>45166</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22758,7 +22758,7 @@
         <v>45593</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>44636</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>45141</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22982,7 +22982,7 @@
         <v>45582</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23055,7 +23055,7 @@
         <v>44516</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>45547</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23206,7 +23206,7 @@
         <v>45191</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>45085</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>45512</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23425,7 +23425,7 @@
         <v>44536</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23498,7 +23498,7 @@
         <v>44581</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
         <v>45230</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
         <v>45090</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>45191</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23790,7 +23790,7 @@
         <v>45678</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23863,7 +23863,7 @@
         <v>45117</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>45434</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24014,7 +24014,7 @@
         <v>45625</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24087,7 +24087,7 @@
         <v>45141</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>44677</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24233,7 +24233,7 @@
         <v>45080</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24306,7 +24306,7 @@
         <v>44818</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24379,7 +24379,7 @@
         <v>45181</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24452,7 +24452,7 @@
         <v>45181</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24530,7 +24530,7 @@
         <v>45160</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>45681</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>45400</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>45181</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24827,7 +24827,7 @@
         <v>45219</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24900,7 +24900,7 @@
         <v>45643</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>44790</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25046,7 +25046,7 @@
         <v>45281</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>45296</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25197,7 +25197,7 @@
         <v>45306</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25270,7 +25270,7 @@
         <v>45257</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25343,7 +25343,7 @@
         <v>45230</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>45281</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>45240</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25562,7 +25562,7 @@
         <v>45173</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25635,7 +25635,7 @@
         <v>45265</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25708,7 +25708,7 @@
         <v>45268</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>45195</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25859,7 +25859,7 @@
         <v>45236</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -25932,7 +25932,7 @@
         <v>45628</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26005,7 +26005,7 @@
         <v>44935</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>44935</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26151,7 +26151,7 @@
         <v>44553</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26224,7 +26224,7 @@
         <v>44911</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>45000</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>44601</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>44606</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26526,7 +26526,7 @@
         <v>44581</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26599,7 +26599,7 @@
         <v>44531</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>44809</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -26745,7 +26745,7 @@
         <v>45566</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -26818,7 +26818,7 @@
         <v>44992</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -26891,7 +26891,7 @@
         <v>44621</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -26964,7 +26964,7 @@
         <v>45014</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27037,7 +27037,7 @@
         <v>45551</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27110,7 +27110,7 @@
         <v>44858</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27183,7 +27183,7 @@
         <v>45002</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27256,7 +27256,7 @@
         <v>45470</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27329,7 +27329,7 @@
         <v>44978</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27402,7 +27402,7 @@
         <v>45721</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>45792</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         <v>45814</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27621,7 +27621,7 @@
         <v>45880</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -27694,7 +27694,7 @@
         <v>46049</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>

--- a/Översikt MARKARYD.xlsx
+++ b/Översikt MARKARYD.xlsx
@@ -601,7 +601,7 @@
         <v>45792</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>45628</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>44743</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>44818</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>45219</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>44818</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>44956</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>45453</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>46090</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v>45823</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>44553</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>45268</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>45347</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>44972</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>45581</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>45762</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>44879</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>44692</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>44595</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>44700</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>44495</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>44846</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>44802</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>44802</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>44802</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>44859</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>44875</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>44638</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>44802</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>44802</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>44582</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>44802</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>44848</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44837</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>44638</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>44700</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>44539</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>44587</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>44642</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>44572</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>44508</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>45119</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>44700</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>44700</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>45281</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>45281</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>45218</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>45008</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>45275</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>44988</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>45771</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>45196</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>45054</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>45512</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>44810</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>44644</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>45236</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>45462</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>44887</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         <v>44578</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>45069</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>45546</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>45414</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         <v>45602</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>45428</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5944,7 +5944,7 @@
         <v>45371</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>44616</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>44823</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>45903</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>44902</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         <v>44760</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>45909</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>46141</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>45837</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>45700</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>45810</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>44911</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>44601</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>44601</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>45917</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>44700</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
         <v>46168</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7200,7 +7200,7 @@
         <v>45678</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>45218</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>45470</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7419,7 +7419,7 @@
         <v>45225</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>45930</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7565,7 +7565,7 @@
         <v>45219</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>44928</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>44956</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
         <v>45372</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         <v>45282</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7930,7 +7930,7 @@
         <v>46175</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
         <v>45217</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>45370</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
         <v>45428</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>45942</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>45426</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         <v>45404</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>45378</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>45265</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         <v>44958</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>45547</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>45195</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>45671</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>45155</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         <v>46190</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>45210</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         <v>44980</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9176,7 +9176,7 @@
         <v>44601</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>45407</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>45352</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>44806</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>46213</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>45040</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>45428</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>44999</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>45230</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>45607</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
         <v>45581</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9989,7 +9989,7 @@
         <v>45783</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10062,7 +10062,7 @@
         <v>45609</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10135,7 +10135,7 @@
         <v>45609</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>45609</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10281,7 +10281,7 @@
         <v>45637</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
         <v>45637</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10437,7 +10437,7 @@
         <v>45265</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>45444</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10583,7 +10583,7 @@
         <v>46013</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>46013</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10729,7 +10729,7 @@
         <v>46013</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10802,7 +10802,7 @@
         <v>45600</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10875,7 +10875,7 @@
         <v>46282</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>46240</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>46021</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11099,7 +11099,7 @@
         <v>46282</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>45593</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
         <v>46240</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         <v>45232</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11401,7 +11401,7 @@
         <v>46281</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>46244</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         <v>46034</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11625,7 +11625,7 @@
         <v>45792</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>45419</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>45275</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>45797</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>46042</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>46288</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>45800</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>45800</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>46290</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>46062</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>46063</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>45237</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>46069</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>46069</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>46069</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>46069</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
         <v>46069</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>44848</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12974,7 +12974,7 @@
         <v>45266</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>46085</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>46085</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         <v>46155</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>46085</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13339,7 +13339,7 @@
         <v>45418</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>46085</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>46085</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>46049</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
         <v>46090</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13709,7 +13709,7 @@
         <v>46090</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>46090</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>46090</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13943,7 +13943,7 @@
         <v>46090</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14021,7 +14021,7 @@
         <v>46090</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>46297</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>46297</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>45842</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>45842</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>45719</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>46297</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>46100</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         <v>45107</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14688,7 +14688,7 @@
         <v>46210</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>46100</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>46100</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>46300</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>46111</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         <v>45530</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15141,7 +15141,7 @@
         <v>45539</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>44835</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         <v>44498</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>45882</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15438,7 +15438,7 @@
         <v>45769</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15511,7 +15511,7 @@
         <v>45170</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>45769</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>44673</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15730,7 +15730,7 @@
         <v>44673</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
         <v>45874</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15876,7 +15876,7 @@
         <v>45085</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15949,7 +15949,7 @@
         <v>45880</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16022,7 +16022,7 @@
         <v>45880</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>45218</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16168,7 +16168,7 @@
         <v>44579</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16241,7 +16241,7 @@
         <v>46133</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16314,7 +16314,7 @@
         <v>44875</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>44498</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16460,7 +16460,7 @@
         <v>44587</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
         <v>45357</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16606,7 +16606,7 @@
         <v>45361</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         <v>45556</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16752,7 +16752,7 @@
         <v>45216</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
         <v>45837</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16898,7 +16898,7 @@
         <v>46267</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>45562</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>45798</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>46269</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>46269</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>44557</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17336,7 +17336,7 @@
         <v>44565</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
         <v>46269</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>45127</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>45666</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17628,7 +17628,7 @@
         <v>44950</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>45026</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>45687</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>45564</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>45923</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>45372</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>45583</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>45532</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18212,7 +18212,7 @@
         <v>45678</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>45678</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18358,7 +18358,7 @@
         <v>45678</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>46317</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>45209</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>44984</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18650,7 +18650,7 @@
         <v>44977</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18723,7 +18723,7 @@
         <v>46149</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18796,7 +18796,7 @@
         <v>45089</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18869,7 +18869,7 @@
         <v>45219</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18942,7 +18942,7 @@
         <v>45707</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19015,7 +19015,7 @@
         <v>45434</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19088,7 +19088,7 @@
         <v>45980</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19161,7 +19161,7 @@
         <v>45282</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         <v>45999</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19307,7 +19307,7 @@
         <v>45267</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>45258</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19453,7 +19453,7 @@
         <v>45079</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19526,7 +19526,7 @@
         <v>45080</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>44984</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19672,7 +19672,7 @@
         <v>44992</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19745,7 +19745,7 @@
         <v>45473</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19818,7 +19818,7 @@
         <v>45680</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19891,7 +19891,7 @@
         <v>44956</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>45678</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20037,7 +20037,7 @@
         <v>45678</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20110,7 +20110,7 @@
         <v>45678</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20183,7 +20183,7 @@
         <v>45663</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20256,7 +20256,7 @@
         <v>45614</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20329,7 +20329,7 @@
         <v>44798</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20402,7 +20402,7 @@
         <v>44977</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20475,7 +20475,7 @@
         <v>45092</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20548,7 +20548,7 @@
         <v>45476</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20621,7 +20621,7 @@
         <v>44839</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>45212</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>45203</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>45075</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -20923,7 +20923,7 @@
         <v>44994</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>45281</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>44844</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>45670</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21220,7 +21220,7 @@
         <v>44902</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21293,7 +21293,7 @@
         <v>45077</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>44970</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21439,7 +21439,7 @@
         <v>45558</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>44915</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21585,7 +21585,7 @@
         <v>45344</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>45265</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
         <v>45054</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>45161</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -21877,7 +21877,7 @@
         <v>45069</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>45281</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>44572</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22096,7 +22096,7 @@
         <v>45258</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22169,7 +22169,7 @@
         <v>45258</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>45063</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
         <v>45329</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>45021</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>44992</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22534,7 +22534,7 @@
         <v>45524</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22612,7 +22612,7 @@
         <v>45306</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -22685,7 +22685,7 @@
         <v>45166</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -22758,7 +22758,7 @@
         <v>45593</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>44636</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>45141</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -22982,7 +22982,7 @@
         <v>45582</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23055,7 +23055,7 @@
         <v>44516</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>45547</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23206,7 +23206,7 @@
         <v>45191</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>45085</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>45512</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23425,7 +23425,7 @@
         <v>44536</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23498,7 +23498,7 @@
         <v>44581</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
         <v>45230</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
         <v>45090</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>45191</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -23790,7 +23790,7 @@
         <v>45678</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -23863,7 +23863,7 @@
         <v>45117</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>45434</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24014,7 +24014,7 @@
         <v>45625</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24087,7 +24087,7 @@
         <v>45141</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>44677</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24233,7 +24233,7 @@
         <v>45080</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24306,7 +24306,7 @@
         <v>44818</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24379,7 +24379,7 @@
         <v>45181</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24452,7 +24452,7 @@
         <v>45181</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24530,7 +24530,7 @@
         <v>45160</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>45681</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>45400</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>45181</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -24827,7 +24827,7 @@
         <v>45219</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -24900,7 +24900,7 @@
         <v>45643</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>44790</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25046,7 +25046,7 @@
         <v>45281</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>45296</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25197,7 +25197,7 @@
         <v>45306</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25270,7 +25270,7 @@
         <v>45257</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25343,7 +25343,7 @@
         <v>45230</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>45281</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>45240</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25562,7 +25562,7 @@
         <v>45173</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25635,7 +25635,7 @@
         <v>45265</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -25708,7 +25708,7 @@
         <v>45268</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>45195</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -25859,7 +25859,7 @@
         <v>45236</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -25932,7 +25932,7 @@
         <v>45628</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26005,7 +26005,7 @@
         <v>44935</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>44935</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26151,7 +26151,7 @@
         <v>44553</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26224,7 +26224,7 @@
         <v>44911</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>45000</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>44601</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>44606</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26526,7 +26526,7 @@
         <v>44581</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26599,7 +26599,7 @@
         <v>44531</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>44809</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -26745,7 +26745,7 @@
         <v>45566</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -26818,7 +26818,7 @@
         <v>44992</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -26891,7 +26891,7 @@
         <v>44621</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -26964,7 +26964,7 @@
         <v>45014</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27037,7 +27037,7 @@
         <v>45551</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27110,7 +27110,7 @@
         <v>44858</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27183,7 +27183,7 @@
         <v>45002</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27256,7 +27256,7 @@
         <v>45470</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27329,7 +27329,7 @@
         <v>44978</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27402,7 +27402,7 @@
         <v>45721</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>45792</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         <v>45814</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -27621,7 +27621,7 @@
         <v>45880</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -27694,7 +27694,7 @@
         <v>46049</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
